--- a/data/nzd0114/nzd0114.xlsx
+++ b/data/nzd0114/nzd0114.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN208"/>
+  <dimension ref="A1:AN209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26419,6 +26419,132 @@
         </is>
       </c>
     </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>279.76</v>
+      </c>
+      <c r="C209" t="n">
+        <v>274.4</v>
+      </c>
+      <c r="D209" t="n">
+        <v>275.52</v>
+      </c>
+      <c r="E209" t="n">
+        <v>275.43</v>
+      </c>
+      <c r="F209" t="n">
+        <v>283.24</v>
+      </c>
+      <c r="G209" t="n">
+        <v>279.04</v>
+      </c>
+      <c r="H209" t="n">
+        <v>277.74</v>
+      </c>
+      <c r="I209" t="n">
+        <v>276.79</v>
+      </c>
+      <c r="J209" t="n">
+        <v>271.05</v>
+      </c>
+      <c r="K209" t="n">
+        <v>278.67</v>
+      </c>
+      <c r="L209" t="n">
+        <v>288.67</v>
+      </c>
+      <c r="M209" t="n">
+        <v>293.99</v>
+      </c>
+      <c r="N209" t="n">
+        <v>314.87</v>
+      </c>
+      <c r="O209" t="n">
+        <v>307.55</v>
+      </c>
+      <c r="P209" t="n">
+        <v>304.9</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>299.33</v>
+      </c>
+      <c r="R209" t="n">
+        <v>294.59</v>
+      </c>
+      <c r="S209" t="n">
+        <v>296.68</v>
+      </c>
+      <c r="T209" t="n">
+        <v>293.55</v>
+      </c>
+      <c r="U209" t="n">
+        <v>301.18</v>
+      </c>
+      <c r="V209" t="n">
+        <v>304.21</v>
+      </c>
+      <c r="W209" t="n">
+        <v>308.79</v>
+      </c>
+      <c r="X209" t="n">
+        <v>324.13</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>334.15</v>
+      </c>
+      <c r="Z209" t="n">
+        <v>327.09</v>
+      </c>
+      <c r="AA209" t="n">
+        <v>317.91</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>316.34</v>
+      </c>
+      <c r="AC209" t="n">
+        <v>312.76</v>
+      </c>
+      <c r="AD209" t="n">
+        <v>303.29</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>301.6</v>
+      </c>
+      <c r="AF209" t="n">
+        <v>303.73</v>
+      </c>
+      <c r="AG209" t="n">
+        <v>293.72</v>
+      </c>
+      <c r="AH209" t="n">
+        <v>281.47</v>
+      </c>
+      <c r="AI209" t="n">
+        <v>266.93</v>
+      </c>
+      <c r="AJ209" t="n">
+        <v>249.11</v>
+      </c>
+      <c r="AK209" t="n">
+        <v>238.43</v>
+      </c>
+      <c r="AL209" t="n">
+        <v>245.52</v>
+      </c>
+      <c r="AM209" t="n">
+        <v>294.72</v>
+      </c>
+      <c r="AN209" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26430,7 +26556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B211"/>
+  <dimension ref="A1:B212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28543,6 +28669,16 @@
       </c>
       <c r="B211" t="n">
         <v>-0.7</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>-0.3</v>
       </c>
     </row>
   </sheetData>
@@ -28711,28 +28847,28 @@
         <v>0.0582</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2609437107435971</v>
+        <v>0.2548637348891277</v>
       </c>
       <c r="J2" t="n">
+        <v>208</v>
+      </c>
+      <c r="K2" t="n">
         <v>207</v>
       </c>
-      <c r="K2" t="n">
-        <v>206</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02773121429786352</v>
+        <v>0.02671683230403499</v>
       </c>
       <c r="M2" t="n">
-        <v>9.494658019968433</v>
+        <v>9.477330035023639</v>
       </c>
       <c r="N2" t="n">
-        <v>128.1771583988785</v>
+        <v>127.7498274498534</v>
       </c>
       <c r="O2" t="n">
-        <v>11.32153516087277</v>
+        <v>11.30264692228565</v>
       </c>
       <c r="P2" t="n">
-        <v>279.1058201058885</v>
+        <v>279.1733541211354</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28789,28 +28925,28 @@
         <v>0.0562</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3832045547708742</v>
+        <v>0.3744709278290823</v>
       </c>
       <c r="J3" t="n">
+        <v>208</v>
+      </c>
+      <c r="K3" t="n">
         <v>207</v>
       </c>
-      <c r="K3" t="n">
-        <v>206</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.04705011582797602</v>
+        <v>0.04536448929488313</v>
       </c>
       <c r="M3" t="n">
-        <v>10.51568520910221</v>
+        <v>10.51142426403909</v>
       </c>
       <c r="N3" t="n">
-        <v>159.6872363705048</v>
+        <v>159.311732491645</v>
       </c>
       <c r="O3" t="n">
-        <v>12.63674152503345</v>
+        <v>12.62187515750513</v>
       </c>
       <c r="P3" t="n">
-        <v>273.2344488747902</v>
+        <v>273.3314586177835</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28867,28 +29003,28 @@
         <v>0.0536</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3304904130280304</v>
+        <v>0.322010826217365</v>
       </c>
       <c r="J4" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K4" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03426360536894901</v>
+        <v>0.03283924569769581</v>
       </c>
       <c r="M4" t="n">
-        <v>10.66137205819977</v>
+        <v>10.6522042982766</v>
       </c>
       <c r="N4" t="n">
-        <v>165.7436350450536</v>
+        <v>165.3141556215878</v>
       </c>
       <c r="O4" t="n">
-        <v>12.8741459928437</v>
+        <v>12.85745525450459</v>
       </c>
       <c r="P4" t="n">
-        <v>275.5067940757752</v>
+        <v>275.600971854317</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28945,28 +29081,28 @@
         <v>0.0601</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2262672023901728</v>
+        <v>0.2131883281043873</v>
       </c>
       <c r="J5" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K5" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01593512651811435</v>
+        <v>0.01424440203232236</v>
       </c>
       <c r="M5" t="n">
-        <v>10.81379770357142</v>
+        <v>10.82674026679323</v>
       </c>
       <c r="N5" t="n">
-        <v>167.2484092987666</v>
+        <v>167.3058553496244</v>
       </c>
       <c r="O5" t="n">
-        <v>12.93245565616858</v>
+        <v>12.93467646868774</v>
       </c>
       <c r="P5" t="n">
-        <v>282.8408681325</v>
+        <v>282.9876102530756</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29023,28 +29159,28 @@
         <v>0.0604</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0560626818032977</v>
+        <v>0.04766972074393373</v>
       </c>
       <c r="J6" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K6" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0009391815007723237</v>
+        <v>0.0006848809448930515</v>
       </c>
       <c r="M6" t="n">
-        <v>11.22080759622482</v>
+        <v>11.20907987493686</v>
       </c>
       <c r="N6" t="n">
-        <v>177.1560389715528</v>
+        <v>176.6476558649158</v>
       </c>
       <c r="O6" t="n">
-        <v>13.30999770742102</v>
+        <v>13.29088619561976</v>
       </c>
       <c r="P6" t="n">
-        <v>290.3703581327941</v>
+        <v>290.464747655417</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29101,28 +29237,28 @@
         <v>0.0414</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2881618109472234</v>
+        <v>0.2767332718277196</v>
       </c>
       <c r="J7" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K7" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01735015801106554</v>
+        <v>0.01614683071965139</v>
       </c>
       <c r="M7" t="n">
-        <v>13.28991230879227</v>
+        <v>13.28175683581974</v>
       </c>
       <c r="N7" t="n">
-        <v>244.083049336671</v>
+        <v>243.5328736596234</v>
       </c>
       <c r="O7" t="n">
-        <v>15.62315747013615</v>
+        <v>15.60553983877595</v>
       </c>
       <c r="P7" t="n">
-        <v>282.871301213511</v>
+        <v>283.0012907155776</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29179,28 +29315,28 @@
         <v>0.0535</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1916099535126202</v>
+        <v>0.1830979131444665</v>
       </c>
       <c r="J8" t="n">
+        <v>208</v>
+      </c>
+      <c r="K8" t="n">
         <v>207</v>
       </c>
-      <c r="K8" t="n">
-        <v>206</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.007795975120671095</v>
+        <v>0.007187058812363367</v>
       </c>
       <c r="M8" t="n">
-        <v>12.88383544395669</v>
+        <v>12.86497673654138</v>
       </c>
       <c r="N8" t="n">
-        <v>246.7806660841539</v>
+        <v>245.9553302843258</v>
       </c>
       <c r="O8" t="n">
-        <v>15.70925415429243</v>
+        <v>15.68296305818278</v>
       </c>
       <c r="P8" t="n">
-        <v>281.3736846006834</v>
+        <v>281.4691240736792</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29257,28 +29393,28 @@
         <v>0.0598</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04473375993657817</v>
+        <v>0.03737339160911499</v>
       </c>
       <c r="J9" t="n">
+        <v>208</v>
+      </c>
+      <c r="K9" t="n">
         <v>207</v>
       </c>
-      <c r="K9" t="n">
-        <v>206</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.0006179775123663633</v>
+        <v>0.0004352495923173327</v>
       </c>
       <c r="M9" t="n">
-        <v>10.90328296835194</v>
+        <v>10.88184330977139</v>
       </c>
       <c r="N9" t="n">
-        <v>170.9126184167899</v>
+        <v>170.3612436140778</v>
       </c>
       <c r="O9" t="n">
-        <v>13.07335528534239</v>
+        <v>13.05225051912802</v>
       </c>
       <c r="P9" t="n">
-        <v>283.1856714822922</v>
+        <v>283.2681980733143</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29335,28 +29471,28 @@
         <v>0.0436</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1910628614226563</v>
+        <v>-0.2035942099254696</v>
       </c>
       <c r="J10" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K10" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01058921752076136</v>
+        <v>0.01207977691181061</v>
       </c>
       <c r="M10" t="n">
-        <v>10.92198117446265</v>
+        <v>10.92512234090835</v>
       </c>
       <c r="N10" t="n">
-        <v>176.6609269630143</v>
+        <v>176.5756908091068</v>
       </c>
       <c r="O10" t="n">
-        <v>13.29138544181961</v>
+        <v>13.28817861142402</v>
       </c>
       <c r="P10" t="n">
-        <v>288.8916626252537</v>
+        <v>289.0338991430202</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29413,28 +29549,28 @@
         <v>0.057</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.03218521765909099</v>
+        <v>-0.04099435282930775</v>
       </c>
       <c r="J11" t="n">
+        <v>208</v>
+      </c>
+      <c r="K11" t="n">
         <v>207</v>
       </c>
-      <c r="K11" t="n">
-        <v>206</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.0003066380762505316</v>
+        <v>0.0005014737770188127</v>
       </c>
       <c r="M11" t="n">
-        <v>11.20888062010625</v>
+        <v>11.19540485793367</v>
       </c>
       <c r="N11" t="n">
-        <v>178.3602567383257</v>
+        <v>177.8915088520528</v>
       </c>
       <c r="O11" t="n">
-        <v>13.35515843179427</v>
+        <v>13.33759756673041</v>
       </c>
       <c r="P11" t="n">
-        <v>288.6177013802629</v>
+        <v>288.7164719666124</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29491,28 +29627,28 @@
         <v>0.0868</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.009333482845386386</v>
+        <v>-0.01635480179984827</v>
       </c>
       <c r="J12" t="n">
+        <v>208</v>
+      </c>
+      <c r="K12" t="n">
         <v>207</v>
       </c>
-      <c r="K12" t="n">
-        <v>206</v>
-      </c>
       <c r="L12" t="n">
-        <v>2.106207333618659e-05</v>
+        <v>6.527073782991444e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>12.40759184047133</v>
+        <v>12.38246697598039</v>
       </c>
       <c r="N12" t="n">
-        <v>218.4347150933684</v>
+        <v>217.629077070059</v>
       </c>
       <c r="O12" t="n">
-        <v>14.7795370392096</v>
+        <v>14.75225667720227</v>
       </c>
       <c r="P12" t="n">
-        <v>296.1617697747788</v>
+        <v>296.2404948455921</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29569,28 +29705,28 @@
         <v>0.0509</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0654046611124976</v>
+        <v>-0.07960216448065512</v>
       </c>
       <c r="J13" t="n">
+        <v>208</v>
+      </c>
+      <c r="K13" t="n">
         <v>207</v>
       </c>
-      <c r="K13" t="n">
-        <v>206</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.0008603001676731337</v>
+        <v>0.001282143846822126</v>
       </c>
       <c r="M13" t="n">
-        <v>13.08844737354709</v>
+        <v>13.08868080910289</v>
       </c>
       <c r="N13" t="n">
-        <v>262.384435083301</v>
+        <v>262.1374288007805</v>
       </c>
       <c r="O13" t="n">
-        <v>16.1982849426506</v>
+        <v>16.19065868952775</v>
       </c>
       <c r="P13" t="n">
-        <v>310.3903374612598</v>
+        <v>310.54952399947</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29647,28 +29783,28 @@
         <v>0.0503</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.001979171922324094</v>
+        <v>-0.0117339221966463</v>
       </c>
       <c r="J14" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K14" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L14" t="n">
-        <v>9.026557394875567e-07</v>
+        <v>3.19904022473283e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>12.15055786427058</v>
+        <v>12.13339519617737</v>
       </c>
       <c r="N14" t="n">
-        <v>229.9452553020039</v>
+        <v>229.3090273130751</v>
       </c>
       <c r="O14" t="n">
-        <v>15.16394590144676</v>
+        <v>15.14295305787729</v>
       </c>
       <c r="P14" t="n">
-        <v>324.9715481266679</v>
+        <v>325.0810633126422</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29725,28 +29861,28 @@
         <v>0.0624</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1009430015830457</v>
+        <v>-0.1150292725074877</v>
       </c>
       <c r="J15" t="n">
+        <v>208</v>
+      </c>
+      <c r="K15" t="n">
         <v>207</v>
       </c>
-      <c r="K15" t="n">
-        <v>206</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.002709675877662354</v>
+        <v>0.003534648357789716</v>
       </c>
       <c r="M15" t="n">
-        <v>11.37250047341512</v>
+        <v>11.37001581028193</v>
       </c>
       <c r="N15" t="n">
-        <v>198.0619955900592</v>
+        <v>198.1097970514881</v>
       </c>
       <c r="O15" t="n">
-        <v>14.07345002442753</v>
+        <v>14.07514820708784</v>
       </c>
       <c r="P15" t="n">
-        <v>324.7918963070613</v>
+        <v>324.949835674752</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29803,28 +29939,28 @@
         <v>0.0615</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.09658908765859395</v>
+        <v>-0.1050753700224367</v>
       </c>
       <c r="J16" t="n">
+        <v>208</v>
+      </c>
+      <c r="K16" t="n">
         <v>207</v>
       </c>
-      <c r="K16" t="n">
-        <v>206</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.002674270108892762</v>
+        <v>0.003190017990900906</v>
       </c>
       <c r="M16" t="n">
-        <v>11.00519091165169</v>
+        <v>10.98846561235065</v>
       </c>
       <c r="N16" t="n">
-        <v>183.7521132230124</v>
+        <v>183.2290463721152</v>
       </c>
       <c r="O16" t="n">
-        <v>13.55551965890693</v>
+        <v>13.53621240865092</v>
       </c>
       <c r="P16" t="n">
-        <v>316.2460757299245</v>
+        <v>316.3412263966823</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29881,28 +30017,28 @@
         <v>0.0573</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2558755974166386</v>
+        <v>-0.2649552264002693</v>
       </c>
       <c r="J17" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K17" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01555319142590617</v>
+        <v>0.01679759839045236</v>
       </c>
       <c r="M17" t="n">
-        <v>12.17779677313824</v>
+        <v>12.15533205868804</v>
       </c>
       <c r="N17" t="n">
-        <v>219.0360374201989</v>
+        <v>218.3912962734456</v>
       </c>
       <c r="O17" t="n">
-        <v>14.79986612845532</v>
+        <v>14.77806808325925</v>
       </c>
       <c r="P17" t="n">
-        <v>315.5556394314281</v>
+        <v>315.6575658944864</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29959,28 +30095,28 @@
         <v>0.0537</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1715661416790262</v>
+        <v>-0.1839739782961342</v>
       </c>
       <c r="J18" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K18" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L18" t="n">
-        <v>0.007178564234553542</v>
+        <v>0.008300876792476486</v>
       </c>
       <c r="M18" t="n">
-        <v>12.05089135962243</v>
+        <v>12.03941733906873</v>
       </c>
       <c r="N18" t="n">
-        <v>215.3665612964786</v>
+        <v>215.0999029829406</v>
       </c>
       <c r="O18" t="n">
-        <v>14.6753726118446</v>
+        <v>14.66628456641083</v>
       </c>
       <c r="P18" t="n">
-        <v>311.9670924613924</v>
+        <v>312.1065374197801</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30037,28 +30173,28 @@
         <v>0.0545</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0564145574207526</v>
+        <v>-0.06924317961411448</v>
       </c>
       <c r="J19" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K19" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0006863910514283145</v>
+        <v>0.001041105927896191</v>
       </c>
       <c r="M19" t="n">
-        <v>12.65043464070426</v>
+        <v>12.63665412886899</v>
       </c>
       <c r="N19" t="n">
-        <v>239.9870128195322</v>
+        <v>239.6314466941647</v>
       </c>
       <c r="O19" t="n">
-        <v>15.49151421971178</v>
+        <v>15.48003380791414</v>
       </c>
       <c r="P19" t="n">
-        <v>311.2095105943055</v>
+        <v>311.3551213039684</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30115,28 +30251,28 @@
         <v>0.0533</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.046686568518708</v>
+        <v>-0.06593611377849656</v>
       </c>
       <c r="J20" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K20" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0004547266704405528</v>
+        <v>0.0009095333132013161</v>
       </c>
       <c r="M20" t="n">
-        <v>12.68658165062491</v>
+        <v>12.70552622168691</v>
       </c>
       <c r="N20" t="n">
-        <v>252.2781910733576</v>
+        <v>252.9013014516865</v>
       </c>
       <c r="O20" t="n">
-        <v>15.88326764470578</v>
+        <v>15.90287085565642</v>
       </c>
       <c r="P20" t="n">
-        <v>314.4627377070415</v>
+        <v>314.6786024503077</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30193,28 +30329,28 @@
         <v>0.0487</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1518085983445286</v>
+        <v>-0.1685780346267175</v>
       </c>
       <c r="J21" t="n">
+        <v>208</v>
+      </c>
+      <c r="K21" t="n">
         <v>207</v>
       </c>
-      <c r="K21" t="n">
-        <v>206</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.005170655199445595</v>
+        <v>0.006396257240153247</v>
       </c>
       <c r="M21" t="n">
-        <v>12.31377013526798</v>
+        <v>12.3186816851798</v>
       </c>
       <c r="N21" t="n">
-        <v>233.2166705891728</v>
+        <v>233.5040788828324</v>
       </c>
       <c r="O21" t="n">
-        <v>15.27143315439559</v>
+        <v>15.2808402544766</v>
       </c>
       <c r="P21" t="n">
-        <v>322.5007089317308</v>
+        <v>322.6891346713349</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -30271,28 +30407,28 @@
         <v>0.0493</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2639188014993888</v>
+        <v>-0.2836877427018835</v>
       </c>
       <c r="J22" t="n">
+        <v>208</v>
+      </c>
+      <c r="K22" t="n">
         <v>207</v>
       </c>
-      <c r="K22" t="n">
-        <v>206</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.01461715557555976</v>
+        <v>0.01689216592466714</v>
       </c>
       <c r="M22" t="n">
-        <v>12.52120423520055</v>
+        <v>12.54117551498966</v>
       </c>
       <c r="N22" t="n">
-        <v>246.9713805030125</v>
+        <v>247.7434396420317</v>
       </c>
       <c r="O22" t="n">
-        <v>15.71532311163256</v>
+        <v>15.7398678406787</v>
       </c>
       <c r="P22" t="n">
-        <v>331.6228985389616</v>
+        <v>331.8450274945561</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -30349,28 +30485,28 @@
         <v>0.0539</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5442762816294769</v>
+        <v>-0.5645848818275514</v>
       </c>
       <c r="J23" t="n">
+        <v>208</v>
+      </c>
+      <c r="K23" t="n">
         <v>207</v>
       </c>
-      <c r="K23" t="n">
-        <v>206</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.05948540654100298</v>
+        <v>0.06384108254823351</v>
       </c>
       <c r="M23" t="n">
-        <v>12.80850541086991</v>
+        <v>12.83605718449414</v>
       </c>
       <c r="N23" t="n">
-        <v>246.3529481719798</v>
+        <v>247.2367503636306</v>
       </c>
       <c r="O23" t="n">
-        <v>15.69563468522314</v>
+        <v>15.72376387394668</v>
       </c>
       <c r="P23" t="n">
-        <v>344.2801024761901</v>
+        <v>344.5082951803606</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -30427,28 +30563,28 @@
         <v>0.0592</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4276739665340758</v>
+        <v>-0.4454097279369343</v>
       </c>
       <c r="J24" t="n">
+        <v>208</v>
+      </c>
+      <c r="K24" t="n">
         <v>207</v>
       </c>
-      <c r="K24" t="n">
-        <v>206</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.03828567280283712</v>
+        <v>0.0415481514061854</v>
       </c>
       <c r="M24" t="n">
-        <v>12.58186474710748</v>
+        <v>12.60085565169557</v>
       </c>
       <c r="N24" t="n">
-        <v>241.6569405240309</v>
+        <v>242.0712379998199</v>
       </c>
       <c r="O24" t="n">
-        <v>15.5453189264174</v>
+        <v>15.5586386936589</v>
       </c>
       <c r="P24" t="n">
-        <v>353.8439311366354</v>
+        <v>354.0432147561644</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -30505,28 +30641,28 @@
         <v>0.0698</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3629617682599025</v>
+        <v>-0.3844128518525223</v>
       </c>
       <c r="J25" t="n">
+        <v>208</v>
+      </c>
+      <c r="K25" t="n">
         <v>207</v>
       </c>
-      <c r="K25" t="n">
-        <v>206</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.03130845305422059</v>
+        <v>0.03497429796923968</v>
       </c>
       <c r="M25" t="n">
-        <v>11.88654612271804</v>
+        <v>11.92339325087834</v>
       </c>
       <c r="N25" t="n">
-        <v>214.3924589652105</v>
+        <v>215.6705637513952</v>
       </c>
       <c r="O25" t="n">
-        <v>14.64214666519942</v>
+        <v>14.68572653127502</v>
       </c>
       <c r="P25" t="n">
-        <v>365.9538499256338</v>
+        <v>366.1948798698272</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -30583,28 +30719,28 @@
         <v>0.0737</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4884339424334977</v>
+        <v>-0.5076239882657948</v>
       </c>
       <c r="J26" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K26" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L26" t="n">
-        <v>0.04776282337972892</v>
+        <v>0.05154010384251462</v>
       </c>
       <c r="M26" t="n">
-        <v>12.77349617207035</v>
+        <v>12.79022525211988</v>
       </c>
       <c r="N26" t="n">
-        <v>250.7243973447691</v>
+        <v>251.3672558497348</v>
       </c>
       <c r="O26" t="n">
-        <v>15.83427918614451</v>
+        <v>15.85456577297956</v>
       </c>
       <c r="P26" t="n">
-        <v>359.9305247769666</v>
+        <v>360.1462080301974</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -30661,28 +30797,28 @@
         <v>0.0769</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.6074538269041424</v>
+        <v>-0.6263161337826876</v>
       </c>
       <c r="J27" t="n">
+        <v>208</v>
+      </c>
+      <c r="K27" t="n">
         <v>207</v>
       </c>
-      <c r="K27" t="n">
-        <v>206</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.06417143655835245</v>
+        <v>0.06820573974850919</v>
       </c>
       <c r="M27" t="n">
-        <v>13.12737845367365</v>
+        <v>13.13969244582321</v>
       </c>
       <c r="N27" t="n">
-        <v>283.0381135075546</v>
+        <v>283.4598201476094</v>
       </c>
       <c r="O27" t="n">
-        <v>16.82373660955124</v>
+        <v>16.83626502962012</v>
       </c>
       <c r="P27" t="n">
-        <v>353.6087028612134</v>
+        <v>353.8206446381714</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -30739,28 +30875,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.6627866038672281</v>
+        <v>-0.6762499018550074</v>
       </c>
       <c r="J28" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K28" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L28" t="n">
-        <v>0.06527400040318576</v>
+        <v>0.06825765673465678</v>
       </c>
       <c r="M28" t="n">
-        <v>14.22017513884962</v>
+        <v>14.21407975231764</v>
       </c>
       <c r="N28" t="n">
-        <v>331.1196474343662</v>
+        <v>330.4261866933235</v>
       </c>
       <c r="O28" t="n">
-        <v>18.19669331044424</v>
+        <v>18.1776287423119</v>
       </c>
       <c r="P28" t="n">
-        <v>347.9591703357731</v>
+        <v>348.1106325437104</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -30817,28 +30953,28 @@
         <v>0.0786</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6009179199750421</v>
+        <v>-0.6143106726978135</v>
       </c>
       <c r="J29" t="n">
+        <v>208</v>
+      </c>
+      <c r="K29" t="n">
         <v>207</v>
       </c>
-      <c r="K29" t="n">
-        <v>206</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.06546657759722585</v>
+        <v>0.06866059076454656</v>
       </c>
       <c r="M29" t="n">
-        <v>13.36081367996557</v>
+        <v>13.35943164588426</v>
       </c>
       <c r="N29" t="n">
-        <v>276.5354133606286</v>
+        <v>276.129630181652</v>
       </c>
       <c r="O29" t="n">
-        <v>16.62935396702556</v>
+        <v>16.61714867784639</v>
       </c>
       <c r="P29" t="n">
-        <v>342.8754663842369</v>
+        <v>343.0243076012027</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -30895,28 +31031,28 @@
         <v>0.0825</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.722740092183383</v>
+        <v>-0.7401037989538566</v>
       </c>
       <c r="J30" t="n">
+        <v>208</v>
+      </c>
+      <c r="K30" t="n">
         <v>207</v>
       </c>
-      <c r="K30" t="n">
-        <v>206</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.08248681706145189</v>
+        <v>0.08657459117471666</v>
       </c>
       <c r="M30" t="n">
-        <v>14.01261069126833</v>
+        <v>14.03101550007534</v>
       </c>
       <c r="N30" t="n">
-        <v>310.1340814202098</v>
+        <v>310.1883826846664</v>
       </c>
       <c r="O30" t="n">
-        <v>17.61062410649349</v>
+        <v>17.61216575792615</v>
       </c>
       <c r="P30" t="n">
-        <v>340.761414947425</v>
+        <v>340.9549748739036</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -30973,28 +31109,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8041049186504813</v>
+        <v>-0.8189884769497374</v>
       </c>
       <c r="J31" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K31" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L31" t="n">
-        <v>0.08414782526504372</v>
+        <v>0.08759576523628843</v>
       </c>
       <c r="M31" t="n">
-        <v>15.63070554644031</v>
+        <v>15.62693721511765</v>
       </c>
       <c r="N31" t="n">
-        <v>376.3244503614938</v>
+        <v>375.6287001688972</v>
       </c>
       <c r="O31" t="n">
-        <v>19.39908375056651</v>
+        <v>19.38114290151376</v>
       </c>
       <c r="P31" t="n">
-        <v>338.6218498696093</v>
+        <v>338.7883993418777</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -31051,28 +31187,28 @@
         <v>0.1625</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6894927637963557</v>
+        <v>-0.7005918099597457</v>
       </c>
       <c r="J32" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K32" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L32" t="n">
-        <v>0.05825759858853696</v>
+        <v>0.06053091175174485</v>
       </c>
       <c r="M32" t="n">
-        <v>16.53321596302649</v>
+        <v>16.50203441851369</v>
       </c>
       <c r="N32" t="n">
-        <v>407.4492410040257</v>
+        <v>406.0652717669959</v>
       </c>
       <c r="O32" t="n">
-        <v>20.18537195604841</v>
+        <v>20.15106130621898</v>
       </c>
       <c r="P32" t="n">
-        <v>333.6428092299509</v>
+        <v>333.7680374862828</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -31129,28 +31265,28 @@
         <v>0.0556</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7877199145553294</v>
+        <v>-0.8043871342679465</v>
       </c>
       <c r="J33" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K33" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L33" t="n">
-        <v>0.06757874886220494</v>
+        <v>0.07076425588632418</v>
       </c>
       <c r="M33" t="n">
-        <v>16.62190907200215</v>
+        <v>16.61471685476711</v>
       </c>
       <c r="N33" t="n">
-        <v>452.14930751753</v>
+        <v>451.2650710875947</v>
       </c>
       <c r="O33" t="n">
-        <v>21.26380275297742</v>
+        <v>21.24300051987936</v>
       </c>
       <c r="P33" t="n">
-        <v>331.5977896880615</v>
+        <v>331.7852815589535</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -31207,28 +31343,28 @@
         <v>0.0582</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.272700892501593</v>
+        <v>-1.288599958084806</v>
       </c>
       <c r="J34" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K34" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1178384281978746</v>
+        <v>0.1213713897057652</v>
       </c>
       <c r="M34" t="n">
-        <v>20.1873067931805</v>
+        <v>20.1683210660211</v>
       </c>
       <c r="N34" t="n">
-        <v>639.9119516124355</v>
+        <v>637.9773856593398</v>
       </c>
       <c r="O34" t="n">
-        <v>25.29648101243403</v>
+        <v>25.25821422150307</v>
       </c>
       <c r="P34" t="n">
-        <v>331.6102808146323</v>
+        <v>331.7889059940445</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -31285,28 +31421,28 @@
         <v>0.0295</v>
       </c>
       <c r="I35" t="n">
-        <v>-2.321430460450148</v>
+        <v>-2.32878884418835</v>
       </c>
       <c r="J35" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K35" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2025416021183478</v>
+        <v>0.2052499753601774</v>
       </c>
       <c r="M35" t="n">
-        <v>26.12241474784213</v>
+        <v>26.02782165347729</v>
       </c>
       <c r="N35" t="n">
-        <v>1113.354823729454</v>
+        <v>1108.138498322628</v>
       </c>
       <c r="O35" t="n">
-        <v>33.36697204916045</v>
+        <v>33.28871427860541</v>
       </c>
       <c r="P35" t="n">
-        <v>336.7029398072295</v>
+        <v>336.7859000356477</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -31363,28 +31499,28 @@
         <v>0.0326</v>
       </c>
       <c r="I36" t="n">
-        <v>-3.585109241882963</v>
+        <v>-3.586202403062157</v>
       </c>
       <c r="J36" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K36" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2403110369333187</v>
+        <v>0.2424506906338054</v>
       </c>
       <c r="M36" t="n">
-        <v>37.31977706861703</v>
+        <v>37.13476214001351</v>
       </c>
       <c r="N36" t="n">
-        <v>2149.214906917998</v>
+        <v>2138.199000265492</v>
       </c>
       <c r="O36" t="n">
-        <v>46.35962582806292</v>
+        <v>46.24066392544004</v>
       </c>
       <c r="P36" t="n">
-        <v>346.4464975216641</v>
+        <v>346.4587400484949</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -31445,28 +31581,28 @@
         <v>0.0211</v>
       </c>
       <c r="I37" t="n">
-        <v>-6.378746492641435</v>
+        <v>-6.348527512616187</v>
       </c>
       <c r="J37" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K37" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3607748281820276</v>
+        <v>0.3608450064226078</v>
       </c>
       <c r="M37" t="n">
-        <v>49.94375357657223</v>
+        <v>49.79636486802557</v>
       </c>
       <c r="N37" t="n">
-        <v>3730.734500723825</v>
+        <v>3715.815895995101</v>
       </c>
       <c r="O37" t="n">
-        <v>61.07973887242663</v>
+        <v>60.95749253369188</v>
       </c>
       <c r="P37" t="n">
-        <v>380.5605005784058</v>
+        <v>380.2155869160622</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -31527,28 +31663,28 @@
         <v>0.0218</v>
       </c>
       <c r="I38" t="n">
-        <v>-2.214789978462561</v>
+        <v>-2.246269123214281</v>
       </c>
       <c r="J38" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K38" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L38" t="n">
-        <v>0.254391274740878</v>
+        <v>0.2607964843963637</v>
       </c>
       <c r="M38" t="n">
-        <v>22.25018611398315</v>
+        <v>22.26096390028171</v>
       </c>
       <c r="N38" t="n">
-        <v>758.3699674418995</v>
+        <v>758.9838306170436</v>
       </c>
       <c r="O38" t="n">
-        <v>27.53851788753163</v>
+        <v>27.54966117063953</v>
       </c>
       <c r="P38" t="n">
-        <v>334.8208783865064</v>
+        <v>335.1742078538023</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -31609,28 +31745,28 @@
         <v>0.0271</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.904731512467444</v>
+        <v>-2.888643600329806</v>
       </c>
       <c r="J39" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K39" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2632388611086782</v>
+        <v>0.2631978755128712</v>
       </c>
       <c r="M39" t="n">
-        <v>25.40561474957701</v>
+        <v>25.34966051269796</v>
       </c>
       <c r="N39" t="n">
-        <v>1167.501438352333</v>
+        <v>1162.16883722017</v>
       </c>
       <c r="O39" t="n">
-        <v>34.16872017433976</v>
+        <v>34.09059748992631</v>
       </c>
       <c r="P39" t="n">
-        <v>358.5602358703126</v>
+        <v>358.3715607423082</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -31672,7 +31808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN208"/>
+  <dimension ref="A1:AN209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73099,6 +73235,208 @@
         </is>
       </c>
     </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>-36.11619115829993,175.42489015558564</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>-36.11684097552128,175.42448386402228</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>-36.11751270521725,175.4241442714846</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>-36.118180336470566,175.42379222426862</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>-36.118922155538456,175.42349912256216</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-36.119703916189714,175.4231968258918</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-36.120468483538154,175.42305721777706</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>-36.12118705847235,175.4229305553524</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>-36.121900746879156,175.4227510361424</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>-36.1226280394974,175.42271894177995</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>-36.12335775018743,175.42271311223124</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>-36.124082686454514,175.42265564051405</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>-36.124873654750346,175.42276530387548</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>-36.125670421739144,175.4227909179756</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>-36.12640950005613,175.42296175035386</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>-36.12712965080722,175.42309493897187</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>-36.12784806961313,175.4232370964424</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>-36.12855228162257,175.42345306618643</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>-36.12926734035863,175.4236126222698</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>-36.12996002093071,175.42388846518216</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>-36.13066225912164,175.42411459512164</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>-36.13136126805232,175.42435747732657</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>-36.13203789791165,175.4247166505913</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>-36.132759014231475,175.42503038022036</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>-36.13345915745019,175.425411148283</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>-36.134135184102874,175.4257623913788</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>-36.134775472646176,175.42618582956408</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>-36.13542484233127,175.42658995384</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>-36.13610083284242,175.42693748135875</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>-36.13674164896522,175.4273597653393</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>-36.13737077883303,175.42782275568473</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>-36.13805925004794,175.42819887022952</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>-36.138739455324234,175.42858884334217</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>-36.139419490751614,175.42894826062735</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>-36.14011612490886,175.4292775332089</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>-36.140776613438675,175.42967242062517</t>
+        </is>
+      </c>
+      <c r="AL209" t="inlineStr">
+        <is>
+          <t>-36.141347148162026,175.43023061465408</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>-36.14170452001275,175.43117580364745</t>
+        </is>
+      </c>
+      <c r="AN209" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0114/nzd0114.xlsx
+++ b/data/nzd0114/nzd0114.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN209"/>
+  <dimension ref="A1:AN210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26531,7 +26531,7 @@
         <v>249.11</v>
       </c>
       <c r="AK209" t="n">
-        <v>238.43</v>
+        <v>224.59</v>
       </c>
       <c r="AL209" t="n">
         <v>245.52</v>
@@ -26542,6 +26542,132 @@
       <c r="AN209" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>280.94</v>
+      </c>
+      <c r="C210" t="n">
+        <v>277.09</v>
+      </c>
+      <c r="D210" t="n">
+        <v>277.16</v>
+      </c>
+      <c r="E210" t="n">
+        <v>277.86</v>
+      </c>
+      <c r="F210" t="n">
+        <v>284.43</v>
+      </c>
+      <c r="G210" t="n">
+        <v>281.14</v>
+      </c>
+      <c r="H210" t="n">
+        <v>280.17</v>
+      </c>
+      <c r="I210" t="n">
+        <v>279.22</v>
+      </c>
+      <c r="J210" t="n">
+        <v>274.9</v>
+      </c>
+      <c r="K210" t="n">
+        <v>280.74</v>
+      </c>
+      <c r="L210" t="n">
+        <v>290.22</v>
+      </c>
+      <c r="M210" t="n">
+        <v>298</v>
+      </c>
+      <c r="N210" t="n">
+        <v>316.05</v>
+      </c>
+      <c r="O210" t="n">
+        <v>309.84</v>
+      </c>
+      <c r="P210" t="n">
+        <v>306.66</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>300.36</v>
+      </c>
+      <c r="R210" t="n">
+        <v>297.49</v>
+      </c>
+      <c r="S210" t="n">
+        <v>300.07</v>
+      </c>
+      <c r="T210" t="n">
+        <v>296.05</v>
+      </c>
+      <c r="U210" t="n">
+        <v>304.01</v>
+      </c>
+      <c r="V210" t="n">
+        <v>306.9</v>
+      </c>
+      <c r="W210" t="n">
+        <v>312.48</v>
+      </c>
+      <c r="X210" t="n">
+        <v>327.43</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>336.42</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>328.05</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>320.15</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>319.72</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>316.16</v>
+      </c>
+      <c r="AD210" t="n">
+        <v>307.84</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>304.58</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>304.43</v>
+      </c>
+      <c r="AG210" t="n">
+        <v>294.67</v>
+      </c>
+      <c r="AH210" t="n">
+        <v>284.71</v>
+      </c>
+      <c r="AI210" t="n">
+        <v>272.53</v>
+      </c>
+      <c r="AJ210" t="n">
+        <v>249.11</v>
+      </c>
+      <c r="AK210" t="n">
+        <v>226.14</v>
+      </c>
+      <c r="AL210" t="n">
+        <v>245.52</v>
+      </c>
+      <c r="AM210" t="n">
+        <v>293.77</v>
+      </c>
+      <c r="AN210" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26556,7 +26682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B212"/>
+  <dimension ref="A1:B213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28679,6 +28805,16 @@
       </c>
       <c r="B212" t="n">
         <v>-0.3</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -28847,28 +28983,28 @@
         <v>0.0582</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2548637348891277</v>
+        <v>0.2500562994755928</v>
       </c>
       <c r="J2" t="n">
+        <v>209</v>
+      </c>
+      <c r="K2" t="n">
         <v>208</v>
       </c>
-      <c r="K2" t="n">
-        <v>207</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02671683230403499</v>
+        <v>0.02597642074748563</v>
       </c>
       <c r="M2" t="n">
-        <v>9.477330035023639</v>
+        <v>9.454335564805723</v>
       </c>
       <c r="N2" t="n">
-        <v>127.7498274498534</v>
+        <v>127.2581923210937</v>
       </c>
       <c r="O2" t="n">
-        <v>11.30264692228565</v>
+        <v>11.28087728508265</v>
       </c>
       <c r="P2" t="n">
-        <v>279.1733541211354</v>
+        <v>279.2268028060031</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28925,28 +29061,28 @@
         <v>0.0562</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3744709278290823</v>
+        <v>0.3685118847146013</v>
       </c>
       <c r="J3" t="n">
+        <v>209</v>
+      </c>
+      <c r="K3" t="n">
         <v>208</v>
       </c>
-      <c r="K3" t="n">
-        <v>207</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.04536448929488313</v>
+        <v>0.04437518426941056</v>
       </c>
       <c r="M3" t="n">
-        <v>10.51142426403909</v>
+        <v>10.49321957002683</v>
       </c>
       <c r="N3" t="n">
-        <v>159.311732491645</v>
+        <v>158.7341009715275</v>
       </c>
       <c r="O3" t="n">
-        <v>12.62187515750513</v>
+        <v>12.59897221885688</v>
       </c>
       <c r="P3" t="n">
-        <v>273.3314586177835</v>
+        <v>273.397710785549</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29003,28 +29139,28 @@
         <v>0.0536</v>
       </c>
       <c r="I4" t="n">
-        <v>0.322010826217365</v>
+        <v>0.315304376773019</v>
       </c>
       <c r="J4" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K4" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03283924569769581</v>
+        <v>0.03179519049837831</v>
       </c>
       <c r="M4" t="n">
-        <v>10.6522042982766</v>
+        <v>10.63456409279483</v>
       </c>
       <c r="N4" t="n">
-        <v>165.3141556215878</v>
+        <v>164.7552066517461</v>
       </c>
       <c r="O4" t="n">
-        <v>12.85745525450459</v>
+        <v>12.83570047374689</v>
       </c>
       <c r="P4" t="n">
-        <v>275.600971854317</v>
+        <v>275.6755260653845</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29081,28 +29217,28 @@
         <v>0.0601</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2131883281043873</v>
+        <v>0.2027960798721282</v>
       </c>
       <c r="J5" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K5" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01424440203232236</v>
+        <v>0.01299502207799974</v>
       </c>
       <c r="M5" t="n">
-        <v>10.82674026679323</v>
+        <v>10.82608270011388</v>
       </c>
       <c r="N5" t="n">
-        <v>167.3058553496244</v>
+        <v>167.0583545536681</v>
       </c>
       <c r="O5" t="n">
-        <v>12.93467646868774</v>
+        <v>12.92510559158679</v>
       </c>
       <c r="P5" t="n">
-        <v>282.9876102530756</v>
+        <v>283.1043159862247</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29159,28 +29295,28 @@
         <v>0.0604</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04766972074393373</v>
+        <v>0.04064839101201288</v>
       </c>
       <c r="J6" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K6" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0006848809448930515</v>
+        <v>0.0005024498502735897</v>
       </c>
       <c r="M6" t="n">
-        <v>11.20907987493686</v>
+        <v>11.19046235057645</v>
       </c>
       <c r="N6" t="n">
-        <v>176.6476558649158</v>
+        <v>176.0433646694708</v>
       </c>
       <c r="O6" t="n">
-        <v>13.29088619561976</v>
+        <v>13.26813342823589</v>
       </c>
       <c r="P6" t="n">
-        <v>290.464747655417</v>
+        <v>290.5437847213313</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29237,28 +29373,28 @@
         <v>0.0414</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2767332718277196</v>
+        <v>0.2676677428474274</v>
       </c>
       <c r="J7" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K7" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01614683071965139</v>
+        <v>0.01525077587780133</v>
       </c>
       <c r="M7" t="n">
-        <v>13.28175683581974</v>
+        <v>13.26186345051208</v>
       </c>
       <c r="N7" t="n">
-        <v>243.5328736596234</v>
+        <v>242.7604486076989</v>
       </c>
       <c r="O7" t="n">
-        <v>15.60553983877595</v>
+        <v>15.58077175905285</v>
       </c>
       <c r="P7" t="n">
-        <v>283.0012907155776</v>
+        <v>283.1044965946685</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29315,28 +29451,28 @@
         <v>0.0535</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1830979131444665</v>
+        <v>0.1771450581719694</v>
       </c>
       <c r="J8" t="n">
+        <v>209</v>
+      </c>
+      <c r="K8" t="n">
         <v>208</v>
       </c>
-      <c r="K8" t="n">
-        <v>207</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.007187058812363367</v>
+        <v>0.006794374511641332</v>
       </c>
       <c r="M8" t="n">
-        <v>12.86497673654138</v>
+        <v>12.83337009341445</v>
       </c>
       <c r="N8" t="n">
-        <v>245.9553302843258</v>
+        <v>244.9561574132046</v>
       </c>
       <c r="O8" t="n">
-        <v>15.68296305818278</v>
+        <v>15.65107527977565</v>
       </c>
       <c r="P8" t="n">
-        <v>281.4691240736792</v>
+        <v>281.535930062002</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29393,28 +29529,28 @@
         <v>0.0598</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03737339160911499</v>
+        <v>0.03254055978497921</v>
       </c>
       <c r="J9" t="n">
+        <v>209</v>
+      </c>
+      <c r="K9" t="n">
         <v>208</v>
       </c>
-      <c r="K9" t="n">
-        <v>207</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.0004352495923173327</v>
+        <v>0.0003331645088214819</v>
       </c>
       <c r="M9" t="n">
-        <v>10.88184330977139</v>
+        <v>10.84989319413296</v>
       </c>
       <c r="N9" t="n">
-        <v>170.3612436140778</v>
+        <v>169.6630156902781</v>
       </c>
       <c r="O9" t="n">
-        <v>13.05225051912802</v>
+        <v>13.02547564161394</v>
       </c>
       <c r="P9" t="n">
-        <v>283.2681980733143</v>
+        <v>283.3224345880457</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29471,28 +29607,28 @@
         <v>0.0436</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2035942099254696</v>
+        <v>-0.2120225871850298</v>
       </c>
       <c r="J10" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K10" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01207977691181061</v>
+        <v>0.0131954041319573</v>
       </c>
       <c r="M10" t="n">
-        <v>10.92512234090835</v>
+        <v>10.91025343989696</v>
       </c>
       <c r="N10" t="n">
-        <v>176.5756908091068</v>
+        <v>176.0796910928156</v>
       </c>
       <c r="O10" t="n">
-        <v>13.28817861142402</v>
+        <v>13.26950229258112</v>
       </c>
       <c r="P10" t="n">
-        <v>289.0338991430202</v>
+        <v>289.129650818703</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29549,28 +29685,28 @@
         <v>0.057</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.04099435282930775</v>
+        <v>-0.04756906968612656</v>
       </c>
       <c r="J11" t="n">
+        <v>209</v>
+      </c>
+      <c r="K11" t="n">
         <v>208</v>
       </c>
-      <c r="K11" t="n">
-        <v>207</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.0005014737770188127</v>
+        <v>0.0006812139694485353</v>
       </c>
       <c r="M11" t="n">
-        <v>11.19540485793367</v>
+        <v>11.17172951070204</v>
       </c>
       <c r="N11" t="n">
-        <v>177.8915088520528</v>
+        <v>177.2598639188051</v>
       </c>
       <c r="O11" t="n">
-        <v>13.33759756673041</v>
+        <v>13.31389739778721</v>
       </c>
       <c r="P11" t="n">
-        <v>288.7164719666124</v>
+        <v>288.7902568075992</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29627,28 +29763,28 @@
         <v>0.0868</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.01635480179984827</v>
+        <v>-0.02169796820307012</v>
       </c>
       <c r="J12" t="n">
+        <v>209</v>
+      </c>
+      <c r="K12" t="n">
         <v>208</v>
       </c>
-      <c r="K12" t="n">
-        <v>207</v>
-      </c>
       <c r="L12" t="n">
-        <v>6.527073782991444e-05</v>
+        <v>0.0001159867533644388</v>
       </c>
       <c r="M12" t="n">
-        <v>12.38246697598039</v>
+        <v>12.34925164813933</v>
       </c>
       <c r="N12" t="n">
-        <v>217.629077070059</v>
+        <v>216.730462974891</v>
       </c>
       <c r="O12" t="n">
-        <v>14.75225667720227</v>
+        <v>14.721768337224</v>
       </c>
       <c r="P12" t="n">
-        <v>296.2404948455921</v>
+        <v>296.3004585964293</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29705,28 +29841,28 @@
         <v>0.0509</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.07960216448065512</v>
+        <v>-0.08956288538384161</v>
       </c>
       <c r="J13" t="n">
+        <v>209</v>
+      </c>
+      <c r="K13" t="n">
         <v>208</v>
       </c>
-      <c r="K13" t="n">
-        <v>207</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.001282143846822126</v>
+        <v>0.001636048010111524</v>
       </c>
       <c r="M13" t="n">
-        <v>13.08868080910289</v>
+        <v>13.07036056281703</v>
       </c>
       <c r="N13" t="n">
-        <v>262.1374288007805</v>
+        <v>261.3903737827462</v>
       </c>
       <c r="O13" t="n">
-        <v>16.19065868952775</v>
+        <v>16.16757167241717</v>
       </c>
       <c r="P13" t="n">
-        <v>310.54952399947</v>
+        <v>310.6613083126139</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29783,28 +29919,28 @@
         <v>0.0503</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0117339221966463</v>
+        <v>-0.0200868926173244</v>
       </c>
       <c r="J14" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K14" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L14" t="n">
-        <v>3.19904022473283e-05</v>
+        <v>9.455420635640088e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>12.13339519617737</v>
+        <v>12.11039832424128</v>
       </c>
       <c r="N14" t="n">
-        <v>229.3090273130751</v>
+        <v>228.559526258478</v>
       </c>
       <c r="O14" t="n">
-        <v>15.14295305787729</v>
+        <v>15.11818528324342</v>
       </c>
       <c r="P14" t="n">
-        <v>325.0810633126422</v>
+        <v>325.1749275082571</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29861,28 +29997,28 @@
         <v>0.0624</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1150292725074877</v>
+        <v>-0.1265303623208199</v>
       </c>
       <c r="J15" t="n">
+        <v>209</v>
+      </c>
+      <c r="K15" t="n">
         <v>208</v>
       </c>
-      <c r="K15" t="n">
-        <v>207</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.003534648357789716</v>
+        <v>0.00430268812673118</v>
       </c>
       <c r="M15" t="n">
-        <v>11.37001581028193</v>
+        <v>11.35922016675935</v>
       </c>
       <c r="N15" t="n">
-        <v>198.1097970514881</v>
+        <v>197.8415742497344</v>
       </c>
       <c r="O15" t="n">
-        <v>14.07514820708784</v>
+        <v>14.06561673904612</v>
       </c>
       <c r="P15" t="n">
-        <v>324.949835674752</v>
+        <v>325.0789067969815</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29939,28 +30075,28 @@
         <v>0.0615</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1050753700224367</v>
+        <v>-0.1116366214328964</v>
       </c>
       <c r="J16" t="n">
+        <v>209</v>
+      </c>
+      <c r="K16" t="n">
         <v>208</v>
       </c>
-      <c r="K16" t="n">
-        <v>207</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.003190017990900906</v>
+        <v>0.00363197092675549</v>
       </c>
       <c r="M16" t="n">
-        <v>10.98846561235065</v>
+        <v>10.96370180838867</v>
       </c>
       <c r="N16" t="n">
-        <v>183.2290463721152</v>
+        <v>182.5708252330336</v>
       </c>
       <c r="O16" t="n">
-        <v>13.53621240865092</v>
+        <v>13.51187719130963</v>
       </c>
       <c r="P16" t="n">
-        <v>316.3412263966823</v>
+        <v>316.4148601215311</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30017,28 +30153,28 @@
         <v>0.0573</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2649552264002693</v>
+        <v>-0.2727889442565469</v>
       </c>
       <c r="J17" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K17" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01679759839045236</v>
+        <v>0.01794179490661907</v>
       </c>
       <c r="M17" t="n">
-        <v>12.15533205868804</v>
+        <v>12.12801012283533</v>
       </c>
       <c r="N17" t="n">
-        <v>218.3912962734456</v>
+        <v>217.6545654638469</v>
       </c>
       <c r="O17" t="n">
-        <v>14.77806808325925</v>
+        <v>14.75312053308882</v>
       </c>
       <c r="P17" t="n">
-        <v>315.6575658944864</v>
+        <v>315.7455865796268</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30095,28 +30231,28 @@
         <v>0.0537</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1839739782961342</v>
+        <v>-0.1932473539687023</v>
       </c>
       <c r="J18" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K18" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L18" t="n">
-        <v>0.008300876792476486</v>
+        <v>0.009225054873435168</v>
       </c>
       <c r="M18" t="n">
-        <v>12.03941733906873</v>
+        <v>12.01607713042205</v>
       </c>
       <c r="N18" t="n">
-        <v>215.0999029829406</v>
+        <v>214.5030661459819</v>
       </c>
       <c r="O18" t="n">
-        <v>14.66628456641083</v>
+        <v>14.64592319200063</v>
       </c>
       <c r="P18" t="n">
-        <v>312.1065374197801</v>
+        <v>312.210851969282</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30173,28 +30309,28 @@
         <v>0.0545</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.06924317961411448</v>
+        <v>-0.07841284950320949</v>
       </c>
       <c r="J19" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K19" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L19" t="n">
-        <v>0.001041105927896191</v>
+        <v>0.00134622102756321</v>
       </c>
       <c r="M19" t="n">
-        <v>12.63665412886899</v>
+        <v>12.60988235022177</v>
       </c>
       <c r="N19" t="n">
-        <v>239.6314466941647</v>
+        <v>238.8963933334482</v>
       </c>
       <c r="O19" t="n">
-        <v>15.48003380791414</v>
+        <v>15.45627359144009</v>
       </c>
       <c r="P19" t="n">
-        <v>311.3551213039684</v>
+        <v>311.4592945309491</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30251,28 +30387,28 @@
         <v>0.0533</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.06593611377849656</v>
+        <v>-0.08222685479691745</v>
       </c>
       <c r="J20" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K20" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0009095333132013161</v>
+        <v>0.001420901395351226</v>
       </c>
       <c r="M20" t="n">
-        <v>12.70552622168691</v>
+        <v>12.71318684686363</v>
       </c>
       <c r="N20" t="n">
-        <v>252.9013014516865</v>
+        <v>253.0320115582526</v>
       </c>
       <c r="O20" t="n">
-        <v>15.90287085565642</v>
+        <v>15.90697996347052</v>
       </c>
       <c r="P20" t="n">
-        <v>314.6786024503077</v>
+        <v>314.8614524096865</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30329,28 +30465,28 @@
         <v>0.0487</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1685780346267175</v>
+        <v>-0.1821617054866719</v>
       </c>
       <c r="J21" t="n">
+        <v>209</v>
+      </c>
+      <c r="K21" t="n">
         <v>208</v>
       </c>
-      <c r="K21" t="n">
-        <v>207</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.006396257240153247</v>
+        <v>0.007506837234101171</v>
       </c>
       <c r="M21" t="n">
-        <v>12.3186816851798</v>
+        <v>12.31397923404008</v>
       </c>
       <c r="N21" t="n">
-        <v>233.5040788828324</v>
+        <v>233.3294462772912</v>
       </c>
       <c r="O21" t="n">
-        <v>15.2808402544766</v>
+        <v>15.27512508221426</v>
       </c>
       <c r="P21" t="n">
-        <v>322.6891346713349</v>
+        <v>322.8419027845385</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -30407,28 +30543,28 @@
         <v>0.0493</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2836877427018835</v>
+        <v>-0.30031708680354</v>
       </c>
       <c r="J22" t="n">
+        <v>209</v>
+      </c>
+      <c r="K22" t="n">
         <v>208</v>
       </c>
-      <c r="K22" t="n">
-        <v>207</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.01689216592466714</v>
+        <v>0.01897665636694201</v>
       </c>
       <c r="M22" t="n">
-        <v>12.54117551498966</v>
+        <v>12.54828773974367</v>
       </c>
       <c r="N22" t="n">
-        <v>247.7434396420317</v>
+        <v>247.9731118062096</v>
       </c>
       <c r="O22" t="n">
-        <v>15.7398678406787</v>
+        <v>15.74716202387622</v>
       </c>
       <c r="P22" t="n">
-        <v>331.8450274945561</v>
+        <v>332.0320486281227</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -30485,28 +30621,28 @@
         <v>0.0539</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5645848818275514</v>
+        <v>-0.5807686540058392</v>
       </c>
       <c r="J23" t="n">
+        <v>209</v>
+      </c>
+      <c r="K23" t="n">
         <v>208</v>
       </c>
-      <c r="K23" t="n">
-        <v>207</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.06384108254823351</v>
+        <v>0.06760842585540117</v>
       </c>
       <c r="M23" t="n">
-        <v>12.83605718449414</v>
+        <v>12.84591960716033</v>
       </c>
       <c r="N23" t="n">
-        <v>247.2367503636306</v>
+        <v>247.3937426786459</v>
       </c>
       <c r="O23" t="n">
-        <v>15.72376387394668</v>
+        <v>15.72875528065225</v>
       </c>
       <c r="P23" t="n">
-        <v>344.5082951803606</v>
+        <v>344.6903052103211</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -30563,28 +30699,28 @@
         <v>0.0592</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4454097279369343</v>
+        <v>-0.4594727605524598</v>
       </c>
       <c r="J24" t="n">
+        <v>209</v>
+      </c>
+      <c r="K24" t="n">
         <v>208</v>
       </c>
-      <c r="K24" t="n">
-        <v>207</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.0415481514061854</v>
+        <v>0.04435308116947956</v>
       </c>
       <c r="M24" t="n">
-        <v>12.60085565169557</v>
+        <v>12.60332522706306</v>
       </c>
       <c r="N24" t="n">
-        <v>242.0712379998199</v>
+        <v>241.9235055183232</v>
       </c>
       <c r="O24" t="n">
-        <v>15.5586386936589</v>
+        <v>15.55389036602493</v>
       </c>
       <c r="P24" t="n">
-        <v>354.0432147561644</v>
+        <v>354.2013739887271</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -30641,28 +30777,28 @@
         <v>0.0698</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3844128518525223</v>
+        <v>-0.4030835175074005</v>
       </c>
       <c r="J25" t="n">
+        <v>209</v>
+      </c>
+      <c r="K25" t="n">
         <v>208</v>
       </c>
-      <c r="K25" t="n">
-        <v>207</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.03497429796923968</v>
+        <v>0.03839417223850738</v>
       </c>
       <c r="M25" t="n">
-        <v>11.92339325087834</v>
+        <v>11.95120173206669</v>
       </c>
       <c r="N25" t="n">
-        <v>215.6705637513952</v>
+        <v>216.4246462046882</v>
       </c>
       <c r="O25" t="n">
-        <v>14.68572653127502</v>
+        <v>14.71137812051231</v>
       </c>
       <c r="P25" t="n">
-        <v>366.1948798698272</v>
+        <v>366.4048586298956</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -30719,28 +30855,28 @@
         <v>0.0737</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5076239882657948</v>
+        <v>-0.5253467296536832</v>
       </c>
       <c r="J26" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K26" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L26" t="n">
-        <v>0.05154010384251462</v>
+        <v>0.05519911587549498</v>
       </c>
       <c r="M26" t="n">
-        <v>12.79022525211988</v>
+        <v>12.8006538054138</v>
       </c>
       <c r="N26" t="n">
-        <v>251.3672558497348</v>
+        <v>251.7737474992768</v>
       </c>
       <c r="O26" t="n">
-        <v>15.85456577297956</v>
+        <v>15.8673799821923</v>
       </c>
       <c r="P26" t="n">
-        <v>360.1462080301974</v>
+        <v>360.3455817011538</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -30797,28 +30933,28 @@
         <v>0.0769</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.6263161337826876</v>
+        <v>-0.642478468814951</v>
       </c>
       <c r="J27" t="n">
+        <v>209</v>
+      </c>
+      <c r="K27" t="n">
         <v>208</v>
       </c>
-      <c r="K27" t="n">
-        <v>207</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.06820573974850919</v>
+        <v>0.07188588609846924</v>
       </c>
       <c r="M27" t="n">
-        <v>13.13969244582321</v>
+        <v>13.14098176146313</v>
       </c>
       <c r="N27" t="n">
-        <v>283.4598201476094</v>
+        <v>283.4391005850778</v>
       </c>
       <c r="O27" t="n">
-        <v>16.83626502962012</v>
+        <v>16.8356496929901</v>
       </c>
       <c r="P27" t="n">
-        <v>353.8206446381714</v>
+        <v>354.0024135762808</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -30875,28 +31011,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.6762499018550074</v>
+        <v>-0.6860671385660297</v>
       </c>
       <c r="J28" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K28" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L28" t="n">
-        <v>0.06825765673465678</v>
+        <v>0.07068780823794119</v>
       </c>
       <c r="M28" t="n">
-        <v>14.21407975231764</v>
+        <v>14.1911030809568</v>
       </c>
       <c r="N28" t="n">
-        <v>330.4261866933235</v>
+        <v>329.3264082289645</v>
       </c>
       <c r="O28" t="n">
-        <v>18.1776287423119</v>
+        <v>18.14735265070265</v>
       </c>
       <c r="P28" t="n">
-        <v>348.1106325437104</v>
+        <v>348.2211772879913</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -30953,28 +31089,28 @@
         <v>0.0786</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6143106726978135</v>
+        <v>-0.6241036026140501</v>
       </c>
       <c r="J29" t="n">
+        <v>209</v>
+      </c>
+      <c r="K29" t="n">
         <v>208</v>
       </c>
-      <c r="K29" t="n">
-        <v>207</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.06866059076454656</v>
+        <v>0.07126102591433325</v>
       </c>
       <c r="M29" t="n">
-        <v>13.35943164588426</v>
+        <v>13.34107579747379</v>
       </c>
       <c r="N29" t="n">
-        <v>276.129630181652</v>
+        <v>275.3100990500365</v>
       </c>
       <c r="O29" t="n">
-        <v>16.61714867784639</v>
+        <v>16.59247115561864</v>
       </c>
       <c r="P29" t="n">
-        <v>343.0243076012027</v>
+        <v>343.1332428866986</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -31031,28 +31167,28 @@
         <v>0.0825</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7401037989538566</v>
+        <v>-0.7526503322955568</v>
       </c>
       <c r="J30" t="n">
+        <v>209</v>
+      </c>
+      <c r="K30" t="n">
         <v>208</v>
       </c>
-      <c r="K30" t="n">
-        <v>207</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.08657459117471666</v>
+        <v>0.08988438578845093</v>
       </c>
       <c r="M30" t="n">
-        <v>14.03101550007534</v>
+        <v>14.02534299161085</v>
       </c>
       <c r="N30" t="n">
-        <v>310.1883826846664</v>
+        <v>309.5251546323894</v>
       </c>
       <c r="O30" t="n">
-        <v>17.61216575792615</v>
+        <v>17.59332699157238</v>
       </c>
       <c r="P30" t="n">
-        <v>340.9549748739036</v>
+        <v>341.0949649660447</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -31109,28 +31245,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8189884769497374</v>
+        <v>-0.8306016942924321</v>
       </c>
       <c r="J31" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K31" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L31" t="n">
-        <v>0.08759576523628843</v>
+        <v>0.09054901615571886</v>
       </c>
       <c r="M31" t="n">
-        <v>15.62693721511765</v>
+        <v>15.607161757029</v>
       </c>
       <c r="N31" t="n">
-        <v>375.6287001688972</v>
+        <v>374.5109071279672</v>
       </c>
       <c r="O31" t="n">
-        <v>19.38114290151376</v>
+        <v>19.3522842870801</v>
       </c>
       <c r="P31" t="n">
-        <v>338.7883993418777</v>
+        <v>338.9184750403932</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -31187,28 +31323,28 @@
         <v>0.1625</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7005918099597457</v>
+        <v>-0.7106959542000288</v>
       </c>
       <c r="J32" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K32" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L32" t="n">
-        <v>0.06053091175174485</v>
+        <v>0.0626970148479753</v>
       </c>
       <c r="M32" t="n">
-        <v>16.50203441851369</v>
+        <v>16.46683931503929</v>
       </c>
       <c r="N32" t="n">
-        <v>406.0652717669959</v>
+        <v>404.6009183662457</v>
       </c>
       <c r="O32" t="n">
-        <v>20.15106130621898</v>
+        <v>20.11469409079456</v>
       </c>
       <c r="P32" t="n">
-        <v>333.7680374862828</v>
+        <v>333.8821475030836</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -31265,28 +31401,28 @@
         <v>0.0556</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8043871342679465</v>
+        <v>-0.8196235748155974</v>
       </c>
       <c r="J33" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K33" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L33" t="n">
-        <v>0.07076425588632418</v>
+        <v>0.07380849119817701</v>
       </c>
       <c r="M33" t="n">
-        <v>16.61471685476711</v>
+        <v>16.60171646980578</v>
       </c>
       <c r="N33" t="n">
-        <v>451.2650710875947</v>
+        <v>450.1959159730147</v>
       </c>
       <c r="O33" t="n">
-        <v>21.24300051987936</v>
+        <v>21.21782071686474</v>
       </c>
       <c r="P33" t="n">
-        <v>331.7852815589535</v>
+        <v>331.9568362032432</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -31343,28 +31479,28 @@
         <v>0.0582</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.288599958084806</v>
+        <v>-1.30082991142199</v>
       </c>
       <c r="J34" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K34" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1213713897057652</v>
+        <v>0.1244122263206671</v>
       </c>
       <c r="M34" t="n">
-        <v>20.1683210660211</v>
+        <v>20.13070297036849</v>
       </c>
       <c r="N34" t="n">
-        <v>637.9773856593398</v>
+        <v>635.5746535223631</v>
       </c>
       <c r="O34" t="n">
-        <v>25.25821422150307</v>
+        <v>25.21060597293058</v>
       </c>
       <c r="P34" t="n">
-        <v>331.7889059940445</v>
+        <v>331.926434665288</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -31421,28 +31557,28 @@
         <v>0.0295</v>
       </c>
       <c r="I35" t="n">
-        <v>-2.32878884418835</v>
+        <v>-2.330423826769919</v>
       </c>
       <c r="J35" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K35" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2052499753601774</v>
+        <v>0.2071845702942099</v>
       </c>
       <c r="M35" t="n">
-        <v>26.02782165347729</v>
+        <v>25.90775466920455</v>
       </c>
       <c r="N35" t="n">
-        <v>1108.138498322628</v>
+        <v>1102.719979188525</v>
       </c>
       <c r="O35" t="n">
-        <v>33.28871427860541</v>
+        <v>33.20722781547</v>
       </c>
       <c r="P35" t="n">
-        <v>336.7859000356477</v>
+        <v>336.8043500135127</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -31499,28 +31635,28 @@
         <v>0.0326</v>
       </c>
       <c r="I36" t="n">
-        <v>-3.586202403062157</v>
+        <v>-3.587183464065873</v>
       </c>
       <c r="J36" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K36" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2424506906338054</v>
+        <v>0.2445569897260587</v>
       </c>
       <c r="M36" t="n">
-        <v>37.13476214001351</v>
+        <v>36.95097483157976</v>
       </c>
       <c r="N36" t="n">
-        <v>2138.199000265492</v>
+        <v>2127.294526240501</v>
       </c>
       <c r="O36" t="n">
-        <v>46.24066392544004</v>
+        <v>46.12260320320723</v>
       </c>
       <c r="P36" t="n">
-        <v>346.4587400484949</v>
+        <v>346.4697371770593</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -31581,28 +31717,28 @@
         <v>0.0211</v>
       </c>
       <c r="I37" t="n">
-        <v>-6.348527512616187</v>
+        <v>-6.345737607289541</v>
       </c>
       <c r="J37" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K37" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3608450064226078</v>
+        <v>0.3632368155497835</v>
       </c>
       <c r="M37" t="n">
-        <v>49.79636486802557</v>
+        <v>49.55096306322802</v>
       </c>
       <c r="N37" t="n">
-        <v>3715.815895995101</v>
+        <v>3695.072472366748</v>
       </c>
       <c r="O37" t="n">
-        <v>60.95749253369188</v>
+        <v>60.78710778089996</v>
       </c>
       <c r="P37" t="n">
-        <v>380.2155869160622</v>
+        <v>380.1835655345676</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -31663,28 +31799,28 @@
         <v>0.0218</v>
       </c>
       <c r="I38" t="n">
-        <v>-2.246269123214281</v>
+        <v>-2.27673679757261</v>
       </c>
       <c r="J38" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K38" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2607964843963637</v>
+        <v>0.267064785251928</v>
       </c>
       <c r="M38" t="n">
-        <v>22.26096390028171</v>
+        <v>22.26728961267671</v>
       </c>
       <c r="N38" t="n">
-        <v>758.9838306170436</v>
+        <v>759.4275377405359</v>
       </c>
       <c r="O38" t="n">
-        <v>27.54966117063953</v>
+        <v>27.55771285394592</v>
       </c>
       <c r="P38" t="n">
-        <v>335.1742078538023</v>
+        <v>335.5164964246081</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -31745,28 +31881,28 @@
         <v>0.0271</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.888643600329806</v>
+        <v>-2.874058862809351</v>
       </c>
       <c r="J39" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K39" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2631978755128712</v>
+        <v>0.2633336089041062</v>
       </c>
       <c r="M39" t="n">
-        <v>25.34966051269796</v>
+        <v>25.28726041339354</v>
       </c>
       <c r="N39" t="n">
-        <v>1162.16883722017</v>
+        <v>1156.729879637738</v>
       </c>
       <c r="O39" t="n">
-        <v>34.09059748992631</v>
+        <v>34.01073183037581</v>
       </c>
       <c r="P39" t="n">
-        <v>358.3715607423082</v>
+        <v>358.2003647041856</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -31808,7 +31944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN209"/>
+  <dimension ref="A1:AN210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73418,7 +73554,7 @@
       </c>
       <c r="AK209" t="inlineStr">
         <is>
-          <t>-36.140776613438675,175.42967242062517</t>
+          <t>-36.14084666944138,175.4295452304603</t>
         </is>
       </c>
       <c r="AL209" t="inlineStr">
@@ -73434,6 +73570,208 @@
       <c r="AN209" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>-36.11619514955808,175.42490230136664</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>-36.11685007429509,175.42451155249177</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>-36.1175182524527,175.42416115231993</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>-36.118188555891486,175.42381723692208</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-36.118925454946975,175.42351169697454</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-36.119707236793055,175.4232197859045</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-36.12047095912431,175.42308403180422</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>-36.12118953407058,175.4229573696241</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>-36.12190466915851,175.4227935200432</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>-36.12263014835322,175.42274178398534</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>-36.123359329273015,175.42273021645784</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>-36.12408677169071,175.42269989121397</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>-36.12487358763885,175.42277840918425</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>-36.12566671760383,175.4228159387484</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>-36.12640584082599,175.42298077052192</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>-36.127127509317525,175.42310607019158</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>-36.1278420401465,175.42326843704362</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>-36.128545233329476,175.42348970257572</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>-36.12926214247628,175.42363964049176</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>-36.129954136867624,175.42391905005618</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>-36.13065666609809,175.42414366720575</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>-36.13135359576888,175.42439735720492</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>-36.13203103642651,175.42475231579584</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>-36.13275153897868,175.42505385003565</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>-36.133454854852566,175.42542039887942</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>-36.13412505831125,175.42578391486475</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>-36.134760193471685,175.42621830716408</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>-36.13540947267524,175.4266226238233</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>-36.13608026454732,175.42698120178952</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>-36.13672817779633,175.42738839999805</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>-36.13736754691899,175.42782943301043</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>-36.138054605816286,175.42820773481688</t>
+        </is>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>-36.13872305506363,175.42861861842437</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>-36.139391144531224,175.42899972408102</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>-36.14011612490886,175.4292775332089</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>-36.14083882358035,175.429559475035</t>
+        </is>
+      </c>
+      <c r="AL210" t="inlineStr">
+        <is>
+          <t>-36.141347148162026,175.43023061465408</t>
+        </is>
+      </c>
+      <c r="AM210" t="inlineStr">
+        <is>
+          <t>-36.14170932885751,175.4311670730927</t>
+        </is>
+      </c>
+      <c r="AN210" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0114/nzd0114.xlsx
+++ b/data/nzd0114/nzd0114.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN210"/>
+  <dimension ref="A1:AN211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26671,6 +26671,132 @@
         </is>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>283.62</v>
+      </c>
+      <c r="C211" t="n">
+        <v>279.87</v>
+      </c>
+      <c r="D211" t="n">
+        <v>279.46</v>
+      </c>
+      <c r="E211" t="n">
+        <v>281</v>
+      </c>
+      <c r="F211" t="n">
+        <v>286.22</v>
+      </c>
+      <c r="G211" t="n">
+        <v>283.99</v>
+      </c>
+      <c r="H211" t="n">
+        <v>283.48</v>
+      </c>
+      <c r="I211" t="n">
+        <v>281.52</v>
+      </c>
+      <c r="J211" t="n">
+        <v>278.43</v>
+      </c>
+      <c r="K211" t="n">
+        <v>283.38</v>
+      </c>
+      <c r="L211" t="n">
+        <v>292.24</v>
+      </c>
+      <c r="M211" t="n">
+        <v>301.69</v>
+      </c>
+      <c r="N211" t="n">
+        <v>318.17</v>
+      </c>
+      <c r="O211" t="n">
+        <v>311.39</v>
+      </c>
+      <c r="P211" t="n">
+        <v>309.38</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>302.41</v>
+      </c>
+      <c r="R211" t="n">
+        <v>300.98</v>
+      </c>
+      <c r="S211" t="n">
+        <v>302.01</v>
+      </c>
+      <c r="T211" t="n">
+        <v>298.9</v>
+      </c>
+      <c r="U211" t="n">
+        <v>306.9</v>
+      </c>
+      <c r="V211" t="n">
+        <v>309.72</v>
+      </c>
+      <c r="W211" t="n">
+        <v>316.1</v>
+      </c>
+      <c r="X211" t="n">
+        <v>331.28</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>337.46</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>331.42</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>323.76</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>322.85</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>317.65</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>309.72</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>306.23</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>306.33</v>
+      </c>
+      <c r="AG211" t="n">
+        <v>299.01</v>
+      </c>
+      <c r="AH211" t="n">
+        <v>284.71</v>
+      </c>
+      <c r="AI211" t="n">
+        <v>272.53</v>
+      </c>
+      <c r="AJ211" t="n">
+        <v>249.11</v>
+      </c>
+      <c r="AK211" t="n">
+        <v>226.14</v>
+      </c>
+      <c r="AL211" t="n">
+        <v>245.52</v>
+      </c>
+      <c r="AM211" t="n">
+        <v>293.77</v>
+      </c>
+      <c r="AN211" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26682,7 +26808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B213"/>
+  <dimension ref="A1:B214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28815,6 +28941,16 @@
       </c>
       <c r="B213" t="n">
         <v>0.3</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -28983,28 +29119,28 @@
         <v>0.0582</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2500562994755928</v>
+        <v>0.2478449289836387</v>
       </c>
       <c r="J2" t="n">
+        <v>210</v>
+      </c>
+      <c r="K2" t="n">
         <v>209</v>
       </c>
-      <c r="K2" t="n">
-        <v>208</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02597642074748563</v>
+        <v>0.0257802802931566</v>
       </c>
       <c r="M2" t="n">
-        <v>9.454335564805723</v>
+        <v>9.419327726665415</v>
       </c>
       <c r="N2" t="n">
-        <v>127.2581923210937</v>
+        <v>126.6753551764777</v>
       </c>
       <c r="O2" t="n">
-        <v>11.28087728508265</v>
+        <v>11.25501466798145</v>
       </c>
       <c r="P2" t="n">
-        <v>279.2268028060031</v>
+        <v>279.2515029362519</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29061,28 +29197,28 @@
         <v>0.0562</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3685118847146013</v>
+        <v>0.3652432841398073</v>
       </c>
       <c r="J3" t="n">
+        <v>210</v>
+      </c>
+      <c r="K3" t="n">
         <v>209</v>
       </c>
-      <c r="K3" t="n">
-        <v>208</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.04437518426941056</v>
+        <v>0.04403766599821435</v>
       </c>
       <c r="M3" t="n">
-        <v>10.49321957002683</v>
+        <v>10.46048724789874</v>
       </c>
       <c r="N3" t="n">
-        <v>158.7341009715275</v>
+        <v>158.0315284078056</v>
       </c>
       <c r="O3" t="n">
-        <v>12.59897221885688</v>
+        <v>12.57105916014262</v>
       </c>
       <c r="P3" t="n">
-        <v>273.397710785549</v>
+        <v>273.4342197559918</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29139,28 +29275,28 @@
         <v>0.0536</v>
       </c>
       <c r="I4" t="n">
-        <v>0.315304376773019</v>
+        <v>0.3108654901268222</v>
       </c>
       <c r="J4" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K4" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03179519049837831</v>
+        <v>0.03122054742203395</v>
       </c>
       <c r="M4" t="n">
-        <v>10.63456409279483</v>
+        <v>10.60548686417124</v>
       </c>
       <c r="N4" t="n">
-        <v>164.7552066517461</v>
+        <v>164.068606183635</v>
       </c>
       <c r="O4" t="n">
-        <v>12.83570047374689</v>
+        <v>12.80892681623386</v>
       </c>
       <c r="P4" t="n">
-        <v>275.6755260653845</v>
+        <v>275.7251032967673</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29217,28 +29353,28 @@
         <v>0.0601</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2027960798721282</v>
+        <v>0.1955814450955489</v>
       </c>
       <c r="J5" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K5" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01299502207799974</v>
+        <v>0.012201326447837</v>
       </c>
       <c r="M5" t="n">
-        <v>10.82608270011388</v>
+        <v>10.80937572755336</v>
       </c>
       <c r="N5" t="n">
-        <v>167.0583545536681</v>
+        <v>166.5267391631001</v>
       </c>
       <c r="O5" t="n">
-        <v>12.92510559158679</v>
+        <v>12.90452398049227</v>
       </c>
       <c r="P5" t="n">
-        <v>283.1043159862247</v>
+        <v>283.1857092193</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29295,28 +29431,28 @@
         <v>0.0604</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04064839101201288</v>
+        <v>0.03547017979591897</v>
       </c>
       <c r="J6" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K6" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005024498502735897</v>
+        <v>0.0003862515758065177</v>
       </c>
       <c r="M6" t="n">
-        <v>11.19046235057645</v>
+        <v>11.16244800424255</v>
       </c>
       <c r="N6" t="n">
-        <v>176.0433646694708</v>
+        <v>175.3294367848936</v>
       </c>
       <c r="O6" t="n">
-        <v>13.26813342823589</v>
+        <v>13.24120224091807</v>
       </c>
       <c r="P6" t="n">
-        <v>290.5437847213313</v>
+        <v>290.6023452909918</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29373,28 +29509,28 @@
         <v>0.0414</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2676677428474274</v>
+        <v>0.2615212878647189</v>
       </c>
       <c r="J7" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K7" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01525077587780133</v>
+        <v>0.01470606021260523</v>
       </c>
       <c r="M7" t="n">
-        <v>13.26186345051208</v>
+        <v>13.227468449726</v>
       </c>
       <c r="N7" t="n">
-        <v>242.7604486076989</v>
+        <v>241.7739314965355</v>
       </c>
       <c r="O7" t="n">
-        <v>15.58077175905285</v>
+        <v>15.54908137146808</v>
       </c>
       <c r="P7" t="n">
-        <v>283.1044965946685</v>
+        <v>283.1747883952775</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29451,28 +29587,28 @@
         <v>0.0535</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1771450581719694</v>
+        <v>0.1744472326625739</v>
       </c>
       <c r="J8" t="n">
+        <v>210</v>
+      </c>
+      <c r="K8" t="n">
         <v>209</v>
       </c>
-      <c r="K8" t="n">
-        <v>208</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.006794374511641332</v>
+        <v>0.006656951087895213</v>
       </c>
       <c r="M8" t="n">
-        <v>12.83337009341445</v>
+        <v>12.78553268058021</v>
       </c>
       <c r="N8" t="n">
-        <v>244.9561574132046</v>
+        <v>243.8219506488347</v>
       </c>
       <c r="O8" t="n">
-        <v>15.65107527977565</v>
+        <v>15.61479909088922</v>
       </c>
       <c r="P8" t="n">
-        <v>281.535930062002</v>
+        <v>281.5663447042922</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29529,28 +29665,28 @@
         <v>0.0598</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03254055978497921</v>
+        <v>0.02998404119634198</v>
       </c>
       <c r="J9" t="n">
+        <v>210</v>
+      </c>
+      <c r="K9" t="n">
         <v>209</v>
       </c>
-      <c r="K9" t="n">
-        <v>208</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.0003331645088214819</v>
+        <v>0.0002857494175522168</v>
       </c>
       <c r="M9" t="n">
-        <v>10.84989319413296</v>
+        <v>10.80882080378497</v>
       </c>
       <c r="N9" t="n">
-        <v>169.6630156902781</v>
+        <v>168.885203821004</v>
       </c>
       <c r="O9" t="n">
-        <v>13.02547564161394</v>
+        <v>12.99558401230987</v>
       </c>
       <c r="P9" t="n">
-        <v>283.3224345880457</v>
+        <v>283.3512561697644</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29607,28 +29743,28 @@
         <v>0.0436</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2120225871850298</v>
+        <v>-0.216844367354658</v>
       </c>
       <c r="J10" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K10" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0131954041319573</v>
+        <v>0.01392666776178009</v>
       </c>
       <c r="M10" t="n">
-        <v>10.91025343989696</v>
+        <v>10.87955722538415</v>
       </c>
       <c r="N10" t="n">
-        <v>176.0796910928156</v>
+        <v>175.3505798793803</v>
       </c>
       <c r="O10" t="n">
-        <v>13.26950229258112</v>
+        <v>13.2420005995839</v>
       </c>
       <c r="P10" t="n">
-        <v>289.129650818703</v>
+        <v>289.1846752586833</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29685,28 +29821,28 @@
         <v>0.057</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.04756906968612656</v>
+        <v>-0.05149989272832103</v>
       </c>
       <c r="J11" t="n">
+        <v>210</v>
+      </c>
+      <c r="K11" t="n">
         <v>209</v>
       </c>
-      <c r="K11" t="n">
-        <v>208</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.0006812139694485353</v>
+        <v>0.0008062281720867537</v>
       </c>
       <c r="M11" t="n">
-        <v>11.17172951070204</v>
+        <v>11.13602994735502</v>
       </c>
       <c r="N11" t="n">
-        <v>177.2598639188051</v>
+        <v>176.4920465172154</v>
       </c>
       <c r="O11" t="n">
-        <v>13.31389739778721</v>
+        <v>13.28503091894089</v>
       </c>
       <c r="P11" t="n">
-        <v>288.7902568075992</v>
+        <v>288.8345719704288</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29763,28 +29899,28 @@
         <v>0.0868</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.02169796820307012</v>
+        <v>-0.02500960448259443</v>
       </c>
       <c r="J12" t="n">
+        <v>210</v>
+      </c>
+      <c r="K12" t="n">
         <v>209</v>
       </c>
-      <c r="K12" t="n">
-        <v>208</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.0001159867533644388</v>
+        <v>0.0001556377766461781</v>
       </c>
       <c r="M12" t="n">
-        <v>12.34925164813933</v>
+        <v>12.3062389646489</v>
       </c>
       <c r="N12" t="n">
-        <v>216.730462974891</v>
+        <v>215.7504810270625</v>
       </c>
       <c r="O12" t="n">
-        <v>14.721768337224</v>
+        <v>14.68844719591089</v>
       </c>
       <c r="P12" t="n">
-        <v>296.3004585964293</v>
+        <v>296.3377931951594</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29841,28 +29977,28 @@
         <v>0.0509</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.08956288538384161</v>
+        <v>-0.09580149876582558</v>
       </c>
       <c r="J13" t="n">
+        <v>210</v>
+      </c>
+      <c r="K13" t="n">
         <v>209</v>
       </c>
-      <c r="K13" t="n">
-        <v>208</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.001636048010111524</v>
+        <v>0.001889295150606651</v>
       </c>
       <c r="M13" t="n">
-        <v>13.07036056281703</v>
+        <v>13.0353455583713</v>
       </c>
       <c r="N13" t="n">
-        <v>261.3903737827462</v>
+        <v>260.342009081679</v>
       </c>
       <c r="O13" t="n">
-        <v>16.16757167241717</v>
+        <v>16.13511726271857</v>
       </c>
       <c r="P13" t="n">
-        <v>310.6613083126139</v>
+        <v>310.7316409541207</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29919,28 +30055,28 @@
         <v>0.0503</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0200868926173244</v>
+        <v>-0.02624917868164839</v>
       </c>
       <c r="J14" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K14" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L14" t="n">
-        <v>9.455420635640088e-05</v>
+        <v>0.0001629751206921881</v>
       </c>
       <c r="M14" t="n">
-        <v>12.11039832424128</v>
+        <v>12.07798072313051</v>
       </c>
       <c r="N14" t="n">
-        <v>228.559526258478</v>
+        <v>227.6542256489045</v>
       </c>
       <c r="O14" t="n">
-        <v>15.11818528324342</v>
+        <v>15.08821479330489</v>
       </c>
       <c r="P14" t="n">
-        <v>325.1749275082571</v>
+        <v>325.2444947721984</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29997,28 +30133,28 @@
         <v>0.0624</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1265303623208199</v>
+        <v>-0.1363112834210001</v>
       </c>
       <c r="J15" t="n">
+        <v>210</v>
+      </c>
+      <c r="K15" t="n">
         <v>209</v>
       </c>
-      <c r="K15" t="n">
-        <v>208</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.00430268812673118</v>
+        <v>0.005028805010375947</v>
       </c>
       <c r="M15" t="n">
-        <v>11.35922016675935</v>
+        <v>11.34192232279644</v>
       </c>
       <c r="N15" t="n">
-        <v>197.8415742497344</v>
+        <v>197.3922360180034</v>
       </c>
       <c r="O15" t="n">
-        <v>14.06561673904612</v>
+        <v>14.04963472898863</v>
       </c>
       <c r="P15" t="n">
-        <v>325.0789067969815</v>
+        <v>325.1891745720823</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30075,28 +30211,28 @@
         <v>0.0615</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1116366214328964</v>
+        <v>-0.1154682119141642</v>
       </c>
       <c r="J16" t="n">
+        <v>210</v>
+      </c>
+      <c r="K16" t="n">
         <v>209</v>
       </c>
-      <c r="K16" t="n">
-        <v>208</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.00363197092675549</v>
+        <v>0.003922904949040906</v>
       </c>
       <c r="M16" t="n">
-        <v>10.96370180838867</v>
+        <v>10.9279010292825</v>
       </c>
       <c r="N16" t="n">
-        <v>182.5708252330336</v>
+        <v>181.7735926111927</v>
       </c>
       <c r="O16" t="n">
-        <v>13.51187719130963</v>
+        <v>13.48234373583439</v>
       </c>
       <c r="P16" t="n">
-        <v>316.4148601215311</v>
+        <v>316.4580565601016</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30153,28 +30289,28 @@
         <v>0.0573</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2727889442565469</v>
+        <v>-0.2784882882021517</v>
       </c>
       <c r="J17" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K17" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01794179490661907</v>
+        <v>0.01885971611369874</v>
       </c>
       <c r="M17" t="n">
-        <v>12.12801012283533</v>
+        <v>12.09218526330356</v>
       </c>
       <c r="N17" t="n">
-        <v>217.6545654638469</v>
+        <v>216.7774375558303</v>
       </c>
       <c r="O17" t="n">
-        <v>14.75312053308882</v>
+        <v>14.72336366309786</v>
       </c>
       <c r="P17" t="n">
-        <v>315.7455865796268</v>
+        <v>315.8099192416959</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30231,28 +30367,28 @@
         <v>0.0537</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1932473539687023</v>
+        <v>-0.1989921235733603</v>
       </c>
       <c r="J18" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K18" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L18" t="n">
-        <v>0.009225054873435168</v>
+        <v>0.009867934449974025</v>
       </c>
       <c r="M18" t="n">
-        <v>12.01607713042205</v>
+        <v>11.97941017946499</v>
       </c>
       <c r="N18" t="n">
-        <v>214.5030661459819</v>
+        <v>213.639302548776</v>
       </c>
       <c r="O18" t="n">
-        <v>14.64592319200063</v>
+        <v>14.6164052539869</v>
       </c>
       <c r="P18" t="n">
-        <v>312.210851969282</v>
+        <v>312.2757723349583</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30309,28 +30445,28 @@
         <v>0.0545</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.07841284950320949</v>
+        <v>-0.08551766670071891</v>
       </c>
       <c r="J19" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K19" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L19" t="n">
-        <v>0.00134622102756321</v>
+        <v>0.00161575775486722</v>
       </c>
       <c r="M19" t="n">
-        <v>12.60988235022177</v>
+        <v>12.5754839472869</v>
       </c>
       <c r="N19" t="n">
-        <v>238.8963933334482</v>
+        <v>238.0028026156894</v>
       </c>
       <c r="O19" t="n">
-        <v>15.45627359144009</v>
+        <v>15.42733945357039</v>
       </c>
       <c r="P19" t="n">
-        <v>311.4592945309491</v>
+        <v>311.5403721773166</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30387,28 +30523,28 @@
         <v>0.0533</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.08222685479691745</v>
+        <v>-0.09543533427831812</v>
       </c>
       <c r="J20" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K20" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L20" t="n">
-        <v>0.001420901395351226</v>
+        <v>0.001926251016291514</v>
       </c>
       <c r="M20" t="n">
-        <v>12.71318684686363</v>
+        <v>12.70852546268985</v>
       </c>
       <c r="N20" t="n">
-        <v>253.0320115582526</v>
+        <v>252.7092194146764</v>
       </c>
       <c r="O20" t="n">
-        <v>15.90697996347052</v>
+        <v>15.89683048329686</v>
       </c>
       <c r="P20" t="n">
-        <v>314.8614524096865</v>
+        <v>315.0103786659301</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30465,28 +30601,28 @@
         <v>0.0487</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1821617054866719</v>
+        <v>-0.1926980392999702</v>
       </c>
       <c r="J21" t="n">
+        <v>210</v>
+      </c>
+      <c r="K21" t="n">
         <v>209</v>
       </c>
-      <c r="K21" t="n">
-        <v>208</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.007506837234101171</v>
+        <v>0.008458348345566913</v>
       </c>
       <c r="M21" t="n">
-        <v>12.31397923404008</v>
+        <v>12.29730805143053</v>
       </c>
       <c r="N21" t="n">
-        <v>233.3294462772912</v>
+        <v>232.7861973376276</v>
       </c>
       <c r="O21" t="n">
-        <v>15.27512508221426</v>
+        <v>15.2573325760969</v>
       </c>
       <c r="P21" t="n">
-        <v>322.8419027845385</v>
+        <v>322.960937668049</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -30543,28 +30679,28 @@
         <v>0.0493</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.30031708680354</v>
+        <v>-0.3138947861096779</v>
       </c>
       <c r="J22" t="n">
+        <v>210</v>
+      </c>
+      <c r="K22" t="n">
         <v>209</v>
       </c>
-      <c r="K22" t="n">
-        <v>208</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.01897665636694201</v>
+        <v>0.02082628383600915</v>
       </c>
       <c r="M22" t="n">
-        <v>12.54828773974367</v>
+        <v>12.54305265832516</v>
       </c>
       <c r="N22" t="n">
-        <v>247.9731118062096</v>
+        <v>247.7384450895354</v>
       </c>
       <c r="O22" t="n">
-        <v>15.74716202387622</v>
+        <v>15.73970918058956</v>
       </c>
       <c r="P22" t="n">
-        <v>332.0320486281227</v>
+        <v>332.1854435265652</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -30621,28 +30757,28 @@
         <v>0.0539</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5807686540058392</v>
+        <v>-0.5931102105375496</v>
       </c>
       <c r="J23" t="n">
+        <v>210</v>
+      </c>
+      <c r="K23" t="n">
         <v>209</v>
       </c>
-      <c r="K23" t="n">
-        <v>208</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.06760842585540117</v>
+        <v>0.07077475394068233</v>
       </c>
       <c r="M23" t="n">
-        <v>12.84591960716033</v>
+        <v>12.83861905316592</v>
       </c>
       <c r="N23" t="n">
-        <v>247.3937426786459</v>
+        <v>246.9964281021572</v>
       </c>
       <c r="O23" t="n">
-        <v>15.72875528065225</v>
+        <v>15.71612000788226</v>
       </c>
       <c r="P23" t="n">
-        <v>344.6903052103211</v>
+        <v>344.8297347092457</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -30699,28 +30835,28 @@
         <v>0.0592</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4594727605524598</v>
+        <v>-0.4695225163130446</v>
       </c>
       <c r="J24" t="n">
+        <v>210</v>
+      </c>
+      <c r="K24" t="n">
         <v>209</v>
       </c>
-      <c r="K24" t="n">
-        <v>208</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.04435308116947956</v>
+        <v>0.04658410888740305</v>
       </c>
       <c r="M24" t="n">
-        <v>12.60332522706306</v>
+        <v>12.58736758830006</v>
       </c>
       <c r="N24" t="n">
-        <v>241.9235055183232</v>
+        <v>241.2874208925509</v>
       </c>
       <c r="O24" t="n">
-        <v>15.55389036602493</v>
+        <v>15.53342914145331</v>
       </c>
       <c r="P24" t="n">
-        <v>354.2013739887271</v>
+        <v>354.3149117265653</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -30777,28 +30913,28 @@
         <v>0.0698</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4030835175074005</v>
+        <v>-0.4203434670035522</v>
       </c>
       <c r="J25" t="n">
+        <v>210</v>
+      </c>
+      <c r="K25" t="n">
         <v>209</v>
       </c>
-      <c r="K25" t="n">
-        <v>208</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.03839417223850738</v>
+        <v>0.04174025483110833</v>
       </c>
       <c r="M25" t="n">
-        <v>11.95120173206669</v>
+        <v>11.97257655137785</v>
       </c>
       <c r="N25" t="n">
-        <v>216.4246462046882</v>
+        <v>216.9271904860401</v>
       </c>
       <c r="O25" t="n">
-        <v>14.71137812051231</v>
+        <v>14.72844833938864</v>
       </c>
       <c r="P25" t="n">
-        <v>366.4048586298956</v>
+        <v>366.5998539778104</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -30855,28 +30991,28 @@
         <v>0.0737</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5253467296536832</v>
+        <v>-0.5394406062229575</v>
       </c>
       <c r="J26" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K26" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L26" t="n">
-        <v>0.05519911587549498</v>
+        <v>0.05836511701064806</v>
       </c>
       <c r="M26" t="n">
-        <v>12.8006538054138</v>
+        <v>12.79568026214393</v>
       </c>
       <c r="N26" t="n">
-        <v>251.7737474992768</v>
+        <v>251.5932895268232</v>
       </c>
       <c r="O26" t="n">
-        <v>15.8673799821923</v>
+        <v>15.86169251772405</v>
       </c>
       <c r="P26" t="n">
-        <v>360.3455817011538</v>
+        <v>360.5048575380538</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -30933,28 +31069,28 @@
         <v>0.0769</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.642478468814951</v>
+        <v>-0.6548072958968022</v>
       </c>
       <c r="J27" t="n">
+        <v>210</v>
+      </c>
+      <c r="K27" t="n">
         <v>209</v>
       </c>
-      <c r="K27" t="n">
-        <v>208</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.07188588609846924</v>
+        <v>0.07498424627126854</v>
       </c>
       <c r="M27" t="n">
-        <v>13.14098176146313</v>
+        <v>13.12646972238345</v>
       </c>
       <c r="N27" t="n">
-        <v>283.4391005850778</v>
+        <v>282.8676988107066</v>
       </c>
       <c r="O27" t="n">
-        <v>16.8356496929901</v>
+        <v>16.81867113688553</v>
       </c>
       <c r="P27" t="n">
-        <v>354.0024135762808</v>
+        <v>354.1416992634576</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -31011,28 +31147,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.6860671385660297</v>
+        <v>-0.6926268628917116</v>
       </c>
       <c r="J28" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K28" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L28" t="n">
-        <v>0.07068780823794119</v>
+        <v>0.07259229988339144</v>
       </c>
       <c r="M28" t="n">
-        <v>14.1911030809568</v>
+        <v>14.15293488260147</v>
       </c>
       <c r="N28" t="n">
-        <v>329.3264082289645</v>
+        <v>327.9658454842671</v>
       </c>
       <c r="O28" t="n">
-        <v>18.14735265070265</v>
+        <v>18.10982731790304</v>
       </c>
       <c r="P28" t="n">
-        <v>348.2211772879913</v>
+        <v>348.2953791064867</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -31089,28 +31225,28 @@
         <v>0.0786</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6241036026140501</v>
+        <v>-0.632233245577013</v>
       </c>
       <c r="J29" t="n">
+        <v>210</v>
+      </c>
+      <c r="K29" t="n">
         <v>209</v>
       </c>
-      <c r="K29" t="n">
-        <v>208</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.07126102591433325</v>
+        <v>0.07359837643944489</v>
       </c>
       <c r="M29" t="n">
-        <v>13.34107579747379</v>
+        <v>13.31476380783173</v>
       </c>
       <c r="N29" t="n">
-        <v>275.3100990500365</v>
+        <v>274.3446008192856</v>
       </c>
       <c r="O29" t="n">
-        <v>16.59247115561864</v>
+        <v>16.56335113493902</v>
       </c>
       <c r="P29" t="n">
-        <v>343.1332428866986</v>
+        <v>343.2240960734931</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -31167,28 +31303,28 @@
         <v>0.0825</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7526503322955568</v>
+        <v>-0.7630995543738444</v>
       </c>
       <c r="J30" t="n">
+        <v>210</v>
+      </c>
+      <c r="K30" t="n">
         <v>209</v>
       </c>
-      <c r="K30" t="n">
-        <v>208</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.08988438578845093</v>
+        <v>0.09286613864634108</v>
       </c>
       <c r="M30" t="n">
-        <v>14.02534299161085</v>
+        <v>14.00960868736568</v>
       </c>
       <c r="N30" t="n">
-        <v>309.5251546323894</v>
+        <v>308.6212826111383</v>
       </c>
       <c r="O30" t="n">
-        <v>17.59332699157238</v>
+        <v>17.56762028879092</v>
       </c>
       <c r="P30" t="n">
-        <v>341.0949649660447</v>
+        <v>341.2120928279991</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -31245,28 +31381,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8306016942924321</v>
+        <v>-0.8403383367701542</v>
       </c>
       <c r="J31" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K31" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L31" t="n">
-        <v>0.09054901615571886</v>
+        <v>0.0932285014227171</v>
       </c>
       <c r="M31" t="n">
-        <v>15.607161757029</v>
+        <v>15.57811798354832</v>
       </c>
       <c r="N31" t="n">
-        <v>374.5109071279672</v>
+        <v>373.1974565036057</v>
       </c>
       <c r="O31" t="n">
-        <v>19.3522842870801</v>
+        <v>19.31831919457813</v>
       </c>
       <c r="P31" t="n">
-        <v>338.9184750403932</v>
+        <v>339.0280441474938</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -31323,28 +31459,28 @@
         <v>0.1625</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7106959542000288</v>
+        <v>-0.7187066326436857</v>
       </c>
       <c r="J32" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K32" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0626970148479753</v>
+        <v>0.06458836560340131</v>
       </c>
       <c r="M32" t="n">
-        <v>16.46683931503929</v>
+        <v>16.42233752476417</v>
       </c>
       <c r="N32" t="n">
-        <v>404.6009183662457</v>
+        <v>402.9559556779728</v>
       </c>
       <c r="O32" t="n">
-        <v>20.11469409079456</v>
+        <v>20.07376286793218</v>
       </c>
       <c r="P32" t="n">
-        <v>333.8821475030836</v>
+        <v>333.9730405894148</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -31401,28 +31537,28 @@
         <v>0.0556</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8196235748155974</v>
+        <v>-0.8302208544045693</v>
       </c>
       <c r="J33" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K33" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L33" t="n">
-        <v>0.07380849119817701</v>
+        <v>0.07623055613148966</v>
       </c>
       <c r="M33" t="n">
-        <v>16.60171646980578</v>
+        <v>16.56785809826215</v>
       </c>
       <c r="N33" t="n">
-        <v>450.1959159730147</v>
+        <v>448.5391237589998</v>
       </c>
       <c r="O33" t="n">
-        <v>21.21782071686474</v>
+        <v>21.17874226102673</v>
       </c>
       <c r="P33" t="n">
-        <v>331.9568362032432</v>
+        <v>332.0767067208676</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -31479,28 +31615,28 @@
         <v>0.0582</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.30082991142199</v>
+        <v>-1.312670885414292</v>
       </c>
       <c r="J34" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K34" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1244122263206671</v>
+        <v>0.127439947675952</v>
       </c>
       <c r="M34" t="n">
-        <v>20.13070297036849</v>
+        <v>20.09092048715277</v>
       </c>
       <c r="N34" t="n">
-        <v>635.5746535223631</v>
+        <v>633.1558572508357</v>
       </c>
       <c r="O34" t="n">
-        <v>25.21060597293058</v>
+        <v>25.16258844496797</v>
       </c>
       <c r="P34" t="n">
-        <v>331.926434665288</v>
+        <v>332.0601999667488</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -31557,28 +31693,28 @@
         <v>0.0295</v>
       </c>
       <c r="I35" t="n">
-        <v>-2.330423826769919</v>
+        <v>-2.331777890463646</v>
       </c>
       <c r="J35" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K35" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2071845702942099</v>
+        <v>0.2090938727194985</v>
       </c>
       <c r="M35" t="n">
-        <v>25.90775466920455</v>
+        <v>25.78750388002937</v>
       </c>
       <c r="N35" t="n">
-        <v>1102.719979188525</v>
+        <v>1097.350186972645</v>
       </c>
       <c r="O35" t="n">
-        <v>33.20722781547</v>
+        <v>33.12627638254329</v>
       </c>
       <c r="P35" t="n">
-        <v>336.8043500135127</v>
+        <v>336.8196996589141</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -31635,28 +31771,28 @@
         <v>0.0326</v>
       </c>
       <c r="I36" t="n">
-        <v>-3.587183464065873</v>
+        <v>-3.587747551205174</v>
       </c>
       <c r="J36" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K36" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2445569897260587</v>
+        <v>0.2466314846434728</v>
       </c>
       <c r="M36" t="n">
-        <v>36.95097483157976</v>
+        <v>36.76662302195189</v>
       </c>
       <c r="N36" t="n">
-        <v>2127.294526240501</v>
+        <v>2116.497642154961</v>
       </c>
       <c r="O36" t="n">
-        <v>46.12260320320723</v>
+        <v>46.00540883586365</v>
       </c>
       <c r="P36" t="n">
-        <v>346.4697371770593</v>
+        <v>346.4760892214142</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -31717,28 +31853,28 @@
         <v>0.0211</v>
       </c>
       <c r="I37" t="n">
-        <v>-6.345737607289541</v>
+        <v>-6.328262725760484</v>
       </c>
       <c r="J37" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K37" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3632368155497835</v>
+        <v>0.3643611305315221</v>
       </c>
       <c r="M37" t="n">
-        <v>49.55096306322802</v>
+        <v>49.36026330852344</v>
       </c>
       <c r="N37" t="n">
-        <v>3695.072472366748</v>
+        <v>3677.703744671664</v>
       </c>
       <c r="O37" t="n">
-        <v>60.78710778089996</v>
+        <v>60.64407427499957</v>
       </c>
       <c r="P37" t="n">
-        <v>380.1835655345676</v>
+        <v>379.9830184266667</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -31799,28 +31935,28 @@
         <v>0.0218</v>
       </c>
       <c r="I38" t="n">
-        <v>-2.27673679757261</v>
+        <v>-2.306268804108038</v>
       </c>
       <c r="J38" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K38" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L38" t="n">
-        <v>0.267064785251928</v>
+        <v>0.2732562664743466</v>
       </c>
       <c r="M38" t="n">
-        <v>22.26728961267671</v>
+        <v>22.26857743468602</v>
       </c>
       <c r="N38" t="n">
-        <v>759.4275377405359</v>
+        <v>759.6516561645414</v>
       </c>
       <c r="O38" t="n">
-        <v>27.55771285394592</v>
+        <v>27.56177890058153</v>
       </c>
       <c r="P38" t="n">
-        <v>335.5164964246081</v>
+        <v>335.8497919582442</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -31881,28 +32017,28 @@
         <v>0.0271</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.874058862809351</v>
+        <v>-2.859462982511669</v>
       </c>
       <c r="J39" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K39" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2633336089041062</v>
+        <v>0.2634528765875124</v>
       </c>
       <c r="M39" t="n">
-        <v>25.28726041339354</v>
+        <v>25.22543438417058</v>
       </c>
       <c r="N39" t="n">
-        <v>1156.729879637738</v>
+        <v>1151.363212601784</v>
       </c>
       <c r="O39" t="n">
-        <v>34.01073183037581</v>
+        <v>33.93174343593009</v>
       </c>
       <c r="P39" t="n">
-        <v>358.2003647041856</v>
+        <v>358.0282851519337</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -31944,7 +32080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN210"/>
+  <dimension ref="A1:AN211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73775,6 +73911,208 @@
         </is>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>-36.116204214444735,175.42492988670412</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>-36.11685947748184,175.4245401673477</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>-36.11752603210798,175.42418482666605</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>-36.11819917686356,175.4238495578067</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-36.11893041792023,175.42353061142862</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-36.11971174331902,175.42325094592445</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-36.120474331209266,175.42312055626314</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>-36.12119187722378,175.4229827493887</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>-36.12190826541684,175.4228324728176</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>-36.12263283790206,175.4227709160748</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>-36.1233613871744,175.4227525071282</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>-36.12409053090841,175.42274061068923</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>-36.12487346706205,175.422801954315</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>-36.12566421043508,175.4228328742045</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>-36.12640018564633,175.42301016532332</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>-36.12712324712627,175.42312822455898</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>-36.12783478398463,175.42330615382915</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>-36.12854119978808,175.4235106685298</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>-36.12925621688313,175.42367044126</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>-36.12994812804621,175.42395028336762</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>-36.13065080277232,175.4241741442556</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>-36.13134606901745,175.42443648054618</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>-36.132023031347344,175.42479392519255</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>-36.13274811419177,175.4250646027248</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>-36.13343975093683,175.42545287231923</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>-36.13410873950541,175.42581860225644</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>-36.13474604440621,175.4262483825632</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>-36.13540273714682,175.42663694095896</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>-36.13607176599458,175.42699926648814</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>-36.136720718924856,175.4274042547544</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>-36.137358774579106,175.42784755717742</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>-36.13803338900275,175.42824823197085</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>-36.13872305506363,175.42861861842437</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>-36.139391144531224,175.42899972408102</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>-36.14011612490886,175.4292775332089</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>-36.14083882358035,175.429559475035</t>
+        </is>
+      </c>
+      <c r="AL211" t="inlineStr">
+        <is>
+          <t>-36.141347148162026,175.43023061465408</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>-36.14170932885751,175.4311670730927</t>
+        </is>
+      </c>
+      <c r="AN211" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
